--- a/research/traditional_assets/database/data/singapore/singapore_apparel.xlsx
+++ b/research/traditional_assets/database/data/singapore/singapore_apparel.xlsx
@@ -1266,7 +1266,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1403,22 +1403,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.07930070859665728</v>
+        <v>0.07920324739204297</v>
       </c>
       <c r="C2">
-        <v>41.76021204602515</v>
+        <v>41.40274390645898</v>
       </c>
       <c r="D2">
-        <v>29.76021204602515</v>
+        <v>29.84704390645898</v>
       </c>
       <c r="E2">
-        <v>-34.8</v>
+        <v>-34.3557</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.4443</v>
       </c>
       <c r="G2">
         <v>12</v>
@@ -1439,28 +1439,28 @@
         <v>2.872333333333333</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.02234829</v>
       </c>
       <c r="N2">
-        <v>2.872333333333333</v>
+        <v>2.849985043333333</v>
       </c>
       <c r="O2">
-        <v>0.4882966666666667</v>
+        <v>0.4844974573666667</v>
       </c>
       <c r="P2">
-        <v>2.384036666666666</v>
+        <v>2.365487585966667</v>
       </c>
       <c r="Q2">
-        <v>5.595036666666666</v>
+        <v>5.576487585966666</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.07930070859665728</v>
+        <v>0.07958157312327573</v>
       </c>
       <c r="T2">
-        <v>0.7736884202461267</v>
+        <v>0.7801748989209175</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1477,7 +1477,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>128.5258663339939</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1485,22 +1485,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.07920324739204297</v>
+        <v>0.07910578618742865</v>
       </c>
       <c r="C3">
-        <v>41.40274390645898</v>
+        <v>41.04578395112659</v>
       </c>
       <c r="D3">
-        <v>29.84704390645898</v>
+        <v>29.93438395112659</v>
       </c>
       <c r="E3">
-        <v>-34.3557</v>
+        <v>-33.9114</v>
       </c>
       <c r="F3">
-        <v>0.4443</v>
+        <v>0.8886000000000001</v>
       </c>
       <c r="G3">
         <v>12</v>
@@ -1521,28 +1521,28 @@
         <v>2.872333333333333</v>
       </c>
       <c r="M3">
-        <v>0.02234829</v>
+        <v>0.04469658</v>
       </c>
       <c r="N3">
-        <v>2.849985043333333</v>
+        <v>2.827636753333333</v>
       </c>
       <c r="O3">
-        <v>0.4844974573666667</v>
+        <v>0.4806982480666667</v>
       </c>
       <c r="P3">
-        <v>2.365487585966667</v>
+        <v>2.346938505266666</v>
       </c>
       <c r="Q3">
-        <v>5.576487585966666</v>
+        <v>5.557938505266666</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.07958157312327573</v>
+        <v>0.07986816957900883</v>
       </c>
       <c r="T3">
-        <v>0.7801748989209175</v>
+        <v>0.7867937547115204</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1559,7 +1559,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>128.5258663339939</v>
+        <v>64.26293316699696</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1567,22 +1567,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.07910578618742865</v>
+        <v>0.07900832498281433</v>
       </c>
       <c r="C4">
-        <v>41.04578395112659</v>
+        <v>40.68933665435008</v>
       </c>
       <c r="D4">
-        <v>29.93438395112659</v>
+        <v>30.02223665435008</v>
       </c>
       <c r="E4">
-        <v>-33.9114</v>
+        <v>-33.46709999999999</v>
       </c>
       <c r="F4">
-        <v>0.8886000000000001</v>
+        <v>1.3329</v>
       </c>
       <c r="G4">
         <v>12</v>
@@ -1603,28 +1603,28 @@
         <v>2.872333333333333</v>
       </c>
       <c r="M4">
-        <v>0.04469658</v>
+        <v>0.06704486999999999</v>
       </c>
       <c r="N4">
-        <v>2.827636753333333</v>
+        <v>2.805288463333333</v>
       </c>
       <c r="O4">
-        <v>0.4806982480666667</v>
+        <v>0.4768990387666667</v>
       </c>
       <c r="P4">
-        <v>2.346938505266666</v>
+        <v>2.328389424566666</v>
       </c>
       <c r="Q4">
-        <v>5.557938505266666</v>
+        <v>5.539389424566666</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.07986816957900883</v>
+        <v>0.08016067524001477</v>
       </c>
       <c r="T4">
-        <v>0.7867937547115204</v>
+        <v>0.7935490817555376</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>64.26293316699696</v>
+        <v>42.84195544466465</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1649,22 +1649,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.07900832498281433</v>
+        <v>0.07891086377820002</v>
       </c>
       <c r="C5">
-        <v>40.68933665435008</v>
+        <v>40.33340654313189</v>
       </c>
       <c r="D5">
-        <v>30.02223665435008</v>
+        <v>30.11060654313189</v>
       </c>
       <c r="E5">
-        <v>-33.46709999999999</v>
+        <v>-33.0228</v>
       </c>
       <c r="F5">
-        <v>1.3329</v>
+        <v>1.7772</v>
       </c>
       <c r="G5">
         <v>12</v>
@@ -1685,28 +1685,28 @@
         <v>2.872333333333333</v>
       </c>
       <c r="M5">
-        <v>0.06704486999999999</v>
+        <v>0.08939316</v>
       </c>
       <c r="N5">
-        <v>2.805288463333333</v>
+        <v>2.782940173333333</v>
       </c>
       <c r="O5">
-        <v>0.4768990387666667</v>
+        <v>0.4730998294666666</v>
       </c>
       <c r="P5">
-        <v>2.328389424566666</v>
+        <v>2.309840343866666</v>
       </c>
       <c r="Q5">
-        <v>5.539389424566666</v>
+        <v>5.520840343866666</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08016067524001477</v>
+        <v>0.08045927476895835</v>
       </c>
       <c r="T5">
-        <v>0.7935490817555376</v>
+        <v>0.8004451447796387</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>42.84195544466465</v>
+        <v>32.13146658349848</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1731,22 +1731,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.07891086377820002</v>
+        <v>0.0788134025735857</v>
       </c>
       <c r="C6">
-        <v>40.33340654313189</v>
+        <v>39.9779981979324</v>
       </c>
       <c r="D6">
-        <v>30.11060654313189</v>
+        <v>30.1994981979324</v>
       </c>
       <c r="E6">
-        <v>-33.0228</v>
+        <v>-32.5785</v>
       </c>
       <c r="F6">
-        <v>1.7772</v>
+        <v>2.2215</v>
       </c>
       <c r="G6">
         <v>12</v>
@@ -1767,28 +1767,28 @@
         <v>2.872333333333333</v>
       </c>
       <c r="M6">
-        <v>0.08939316</v>
+        <v>0.11174145</v>
       </c>
       <c r="N6">
-        <v>2.782940173333333</v>
+        <v>2.760591883333333</v>
       </c>
       <c r="O6">
-        <v>0.4730998294666666</v>
+        <v>0.4693006201666667</v>
       </c>
       <c r="P6">
-        <v>2.309840343866666</v>
+        <v>2.291291263166667</v>
       </c>
       <c r="Q6">
-        <v>5.520840343866666</v>
+        <v>5.502291263166667</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08045927476895835</v>
+        <v>0.08076416060377442</v>
       </c>
       <c r="T6">
-        <v>0.8004451447796387</v>
+        <v>0.8074863880779312</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1805,7 +1805,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>32.13146658349848</v>
+        <v>25.70517326679879</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1813,22 +1813,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.0788134025735857</v>
+        <v>0.07871594136897138</v>
       </c>
       <c r="C7">
-        <v>39.9779981979324</v>
+        <v>39.62311625346135</v>
       </c>
       <c r="D7">
-        <v>30.1994981979324</v>
+        <v>30.28891625346135</v>
       </c>
       <c r="E7">
-        <v>-32.5785</v>
+        <v>-32.1342</v>
       </c>
       <c r="F7">
-        <v>2.2215</v>
+        <v>2.6658</v>
       </c>
       <c r="G7">
         <v>12</v>
@@ -1849,28 +1849,28 @@
         <v>2.872333333333333</v>
       </c>
       <c r="M7">
-        <v>0.11174145</v>
+        <v>0.13408974</v>
       </c>
       <c r="N7">
-        <v>2.760591883333333</v>
+        <v>2.738243593333333</v>
       </c>
       <c r="O7">
-        <v>0.4693006201666667</v>
+        <v>0.4655014108666667</v>
       </c>
       <c r="P7">
-        <v>2.291291263166667</v>
+        <v>2.272742182466667</v>
       </c>
       <c r="Q7">
-        <v>5.502291263166667</v>
+        <v>5.483742182466667</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08076416060377442</v>
+        <v>0.08107553337124615</v>
       </c>
       <c r="T7">
-        <v>0.8074863880779312</v>
+        <v>0.8146774450634215</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1887,7 +1887,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>25.70517326679879</v>
+        <v>21.42097772233232</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1895,22 +1895,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.07871594136897138</v>
+        <v>0.07861848016435707</v>
       </c>
       <c r="C8">
-        <v>39.62311625346135</v>
+        <v>39.26876539948336</v>
       </c>
       <c r="D8">
-        <v>30.28891625346135</v>
+        <v>30.37886539948336</v>
       </c>
       <c r="E8">
-        <v>-32.1342</v>
+        <v>-31.6899</v>
       </c>
       <c r="F8">
-        <v>2.6658</v>
+        <v>3.1101</v>
       </c>
       <c r="G8">
         <v>12</v>
@@ -1931,28 +1931,28 @@
         <v>2.872333333333333</v>
       </c>
       <c r="M8">
-        <v>0.13408974</v>
+        <v>0.15643803</v>
       </c>
       <c r="N8">
-        <v>2.738243593333333</v>
+        <v>2.715895303333333</v>
       </c>
       <c r="O8">
-        <v>0.4655014108666667</v>
+        <v>0.4617022015666667</v>
       </c>
       <c r="P8">
-        <v>2.272742182466667</v>
+        <v>2.254193101766667</v>
       </c>
       <c r="Q8">
-        <v>5.483742182466667</v>
+        <v>5.465193101766666</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08107553337124615</v>
+        <v>0.08139360232726567</v>
       </c>
       <c r="T8">
-        <v>0.8146774450634215</v>
+        <v>0.8220231484356966</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>21.42097772233232</v>
+        <v>18.36083804771342</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.07861848016435707</v>
+        <v>0.07852101895974274</v>
       </c>
       <c r="C9">
-        <v>39.26876539948336</v>
+        <v>38.91495038163789</v>
       </c>
       <c r="D9">
-        <v>30.37886539948336</v>
+        <v>30.46935038163789</v>
       </c>
       <c r="E9">
-        <v>-31.6899</v>
+        <v>-31.2456</v>
       </c>
       <c r="F9">
-        <v>3.1101</v>
+        <v>3.5544</v>
       </c>
       <c r="G9">
         <v>12</v>
@@ -2013,28 +2013,28 @@
         <v>2.872333333333333</v>
       </c>
       <c r="M9">
-        <v>0.15643803</v>
+        <v>0.17878632</v>
       </c>
       <c r="N9">
-        <v>2.715895303333333</v>
+        <v>2.693547013333333</v>
       </c>
       <c r="O9">
-        <v>0.4617022015666667</v>
+        <v>0.4579029922666667</v>
       </c>
       <c r="P9">
-        <v>2.254193101766667</v>
+        <v>2.235644021066666</v>
       </c>
       <c r="Q9">
-        <v>5.465193101766666</v>
+        <v>5.446644021066666</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08139360232726567</v>
+        <v>0.08171858582580732</v>
       </c>
       <c r="T9">
-        <v>0.8220231484356966</v>
+        <v>0.8295285410117167</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2051,7 +2051,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>18.36083804771342</v>
+        <v>16.06573329174924</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2059,22 +2059,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.07852101895974274</v>
+        <v>0.07842355775512844</v>
       </c>
       <c r="C10">
-        <v>38.91495038163789</v>
+        <v>38.56167600227373</v>
       </c>
       <c r="D10">
-        <v>30.46935038163789</v>
+        <v>30.56037600227373</v>
       </c>
       <c r="E10">
-        <v>-31.2456</v>
+        <v>-30.8013</v>
       </c>
       <c r="F10">
-        <v>3.5544</v>
+        <v>3.9987</v>
       </c>
       <c r="G10">
         <v>12</v>
@@ -2095,28 +2095,28 @@
         <v>2.872333333333333</v>
       </c>
       <c r="M10">
-        <v>0.17878632</v>
+        <v>0.20113461</v>
       </c>
       <c r="N10">
-        <v>2.693547013333333</v>
+        <v>2.671198723333333</v>
       </c>
       <c r="O10">
-        <v>0.4579029922666667</v>
+        <v>0.4541037829666667</v>
       </c>
       <c r="P10">
-        <v>2.235644021066666</v>
+        <v>2.217094940366667</v>
       </c>
       <c r="Q10">
-        <v>5.446644021066666</v>
+        <v>5.428094940366666</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08171858582580732</v>
+        <v>0.08205071181882245</v>
       </c>
       <c r="T10">
-        <v>0.8295285410117167</v>
+        <v>0.8371988872707263</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2133,7 +2133,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>16.06573329174924</v>
+        <v>14.28065181488821</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2141,22 +2141,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.07842355775512844</v>
+        <v>0.0784505965505141</v>
       </c>
       <c r="C11">
-        <v>38.56167600227373</v>
+        <v>38.09206817206744</v>
       </c>
       <c r="D11">
-        <v>30.56037600227373</v>
+        <v>30.53506817206744</v>
       </c>
       <c r="E11">
-        <v>-30.8013</v>
+        <v>-30.357</v>
       </c>
       <c r="F11">
-        <v>3.9987</v>
+        <v>4.443</v>
       </c>
       <c r="G11">
         <v>12</v>
@@ -2177,45 +2177,45 @@
         <v>2.872333333333333</v>
       </c>
       <c r="M11">
-        <v>0.20113461</v>
+        <v>0.2301474</v>
       </c>
       <c r="N11">
-        <v>2.671198723333333</v>
+        <v>2.642185933333333</v>
       </c>
       <c r="O11">
-        <v>0.4541037829666667</v>
+        <v>0.4491716086666667</v>
       </c>
       <c r="P11">
-        <v>2.217094940366667</v>
+        <v>2.193014324666667</v>
       </c>
       <c r="Q11">
-        <v>5.428094940366666</v>
+        <v>5.404014324666667</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08205071181882245</v>
+        <v>0.08239021838946012</v>
       </c>
       <c r="T11">
-        <v>0.8371988872707263</v>
+        <v>0.845039685668825</v>
       </c>
       <c r="U11">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V11">
         <v>0.17</v>
       </c>
       <c r="W11">
-        <v>0.04174899999999999</v>
+        <v>0.042994</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y11">
-        <v>14.28065181488821</v>
+        <v>12.48040748378358</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2223,22 +2223,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.0784505965505141</v>
+        <v>0.07836558534589978</v>
       </c>
       <c r="C12">
-        <v>38.09206817206744</v>
+        <v>37.72747878990882</v>
       </c>
       <c r="D12">
-        <v>30.53506817206744</v>
+        <v>30.61477878990882</v>
       </c>
       <c r="E12">
-        <v>-30.357</v>
+        <v>-29.9127</v>
       </c>
       <c r="F12">
-        <v>4.443000000000001</v>
+        <v>4.8873</v>
       </c>
       <c r="G12">
         <v>12</v>
@@ -2259,28 +2259,28 @@
         <v>2.872333333333333</v>
       </c>
       <c r="M12">
-        <v>0.2301474</v>
+        <v>0.25316214</v>
       </c>
       <c r="N12">
-        <v>2.642185933333333</v>
+        <v>2.619171193333333</v>
       </c>
       <c r="O12">
-        <v>0.4491716086666667</v>
+        <v>0.4452591028666666</v>
       </c>
       <c r="P12">
-        <v>2.193014324666667</v>
+        <v>2.173912090466666</v>
       </c>
       <c r="Q12">
-        <v>5.404014324666667</v>
+        <v>5.384912090466666</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08239021838946012</v>
+        <v>0.08273735432123572</v>
       </c>
       <c r="T12">
-        <v>0.845039685668825</v>
+        <v>0.8530566817837349</v>
       </c>
       <c r="U12">
         <v>0.0518</v>
@@ -2297,7 +2297,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>12.48040748378358</v>
+        <v>11.3458249852578</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2305,22 +2305,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.07836558534589978</v>
+        <v>0.07828057414128547</v>
       </c>
       <c r="C13">
-        <v>37.72747878990882</v>
+        <v>37.36330665995846</v>
       </c>
       <c r="D13">
-        <v>30.61477878990882</v>
+        <v>30.69490665995846</v>
       </c>
       <c r="E13">
-        <v>-29.9127</v>
+        <v>-29.4684</v>
       </c>
       <c r="F13">
-        <v>4.8873</v>
+        <v>5.3316</v>
       </c>
       <c r="G13">
         <v>12</v>
@@ -2341,28 +2341,28 @@
         <v>2.872333333333333</v>
       </c>
       <c r="M13">
-        <v>0.25316214</v>
+        <v>0.27617688</v>
       </c>
       <c r="N13">
-        <v>2.619171193333333</v>
+        <v>2.596156453333333</v>
       </c>
       <c r="O13">
-        <v>0.4452591028666666</v>
+        <v>0.4413465970666667</v>
       </c>
       <c r="P13">
-        <v>2.173912090466666</v>
+        <v>2.154809856266667</v>
       </c>
       <c r="Q13">
-        <v>5.384912090466666</v>
+        <v>5.365809856266667</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08273735432123572</v>
+        <v>0.08309237970600622</v>
       </c>
       <c r="T13">
-        <v>0.8530566817837349</v>
+        <v>0.8612558823558021</v>
       </c>
       <c r="U13">
         <v>0.0518</v>
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>11.3458249852578</v>
+        <v>10.40033956981965</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2387,22 +2387,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.07828057414128547</v>
+        <v>0.07837899293667117</v>
       </c>
       <c r="C14">
-        <v>37.36330665995846</v>
+        <v>36.8262795537578</v>
       </c>
       <c r="D14">
-        <v>30.69490665995846</v>
+        <v>30.6021795537578</v>
       </c>
       <c r="E14">
-        <v>-29.4684</v>
+        <v>-29.0241</v>
       </c>
       <c r="F14">
-        <v>5.3316</v>
+        <v>5.7759</v>
       </c>
       <c r="G14">
         <v>12</v>
@@ -2423,45 +2423,45 @@
         <v>2.872333333333333</v>
       </c>
       <c r="M14">
-        <v>0.27617688</v>
+        <v>0.30901065</v>
       </c>
       <c r="N14">
-        <v>2.596156453333333</v>
+        <v>2.563322683333333</v>
       </c>
       <c r="O14">
-        <v>0.4413465970666667</v>
+        <v>0.4357648561666667</v>
       </c>
       <c r="P14">
-        <v>2.154809856266667</v>
+        <v>2.127557827166667</v>
       </c>
       <c r="Q14">
-        <v>5.365809856266667</v>
+        <v>5.338557827166666</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.08309237970600622</v>
+        <v>0.0834555665938749</v>
       </c>
       <c r="T14">
-        <v>0.8612558823558021</v>
+        <v>0.8696435702973417</v>
       </c>
       <c r="U14">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V14">
         <v>0.17</v>
       </c>
       <c r="W14">
-        <v>0.042994</v>
+        <v>0.044405</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y14">
-        <v>10.40033956981965</v>
+        <v>9.295256760028606</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2469,22 +2469,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.07837899293667117</v>
+        <v>0.07830809173205684</v>
       </c>
       <c r="C15">
-        <v>36.8262795537578</v>
+        <v>36.44872390196713</v>
       </c>
       <c r="D15">
-        <v>30.6021795537578</v>
+        <v>30.66892390196713</v>
       </c>
       <c r="E15">
-        <v>-29.0241</v>
+        <v>-28.5798</v>
       </c>
       <c r="F15">
-        <v>5.7759</v>
+        <v>6.2202</v>
       </c>
       <c r="G15">
         <v>12</v>
@@ -2505,28 +2505,28 @@
         <v>2.872333333333333</v>
       </c>
       <c r="M15">
-        <v>0.30901065</v>
+        <v>0.3327807</v>
       </c>
       <c r="N15">
-        <v>2.563322683333333</v>
+        <v>2.539552633333333</v>
       </c>
       <c r="O15">
-        <v>0.4357648561666667</v>
+        <v>0.4317239476666667</v>
       </c>
       <c r="P15">
-        <v>2.127557827166667</v>
+        <v>2.107828685666667</v>
       </c>
       <c r="Q15">
-        <v>5.338557827166666</v>
+        <v>5.318828685666666</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.0834555665938749</v>
+        <v>0.08382719968843819</v>
       </c>
       <c r="T15">
-        <v>0.8696435702973417</v>
+        <v>0.87822632074915</v>
       </c>
       <c r="U15">
         <v>0.0535</v>
@@ -2543,7 +2543,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>9.295256760028606</v>
+        <v>8.63130984859799</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2551,22 +2551,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.07830809173205684</v>
+        <v>0.07823719052744253</v>
       </c>
       <c r="C16">
-        <v>36.44872390196713</v>
+        <v>36.07146002974257</v>
       </c>
       <c r="D16">
-        <v>30.66892390196713</v>
+        <v>30.73596002974258</v>
       </c>
       <c r="E16">
-        <v>-28.5798</v>
+        <v>-28.1355</v>
       </c>
       <c r="F16">
-        <v>6.2202</v>
+        <v>6.664500000000001</v>
       </c>
       <c r="G16">
         <v>12</v>
@@ -2587,28 +2587,28 @@
         <v>2.872333333333333</v>
       </c>
       <c r="M16">
-        <v>0.3327807</v>
+        <v>0.3565507500000001</v>
       </c>
       <c r="N16">
-        <v>2.539552633333333</v>
+        <v>2.515782583333333</v>
       </c>
       <c r="O16">
-        <v>0.4317239476666667</v>
+        <v>0.4276830391666666</v>
       </c>
       <c r="P16">
-        <v>2.107828685666667</v>
+        <v>2.088099544166666</v>
       </c>
       <c r="Q16">
-        <v>5.318828685666666</v>
+        <v>5.299099544166666</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.08382719968843819</v>
+        <v>0.08420757709110885</v>
       </c>
       <c r="T16">
-        <v>0.87822632074915</v>
+        <v>0.8870110182704124</v>
       </c>
       <c r="U16">
         <v>0.0535</v>
@@ -2625,7 +2625,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>8.63130984859799</v>
+        <v>8.055889192024789</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2633,22 +2633,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.07823719052744252</v>
+        <v>0.07827252932282822</v>
       </c>
       <c r="C17">
-        <v>36.07146002974259</v>
+        <v>35.59371108612395</v>
       </c>
       <c r="D17">
-        <v>30.73596002974259</v>
+        <v>30.70251108612394</v>
       </c>
       <c r="E17">
-        <v>-28.1355</v>
+        <v>-27.69119999999999</v>
       </c>
       <c r="F17">
-        <v>6.664499999999999</v>
+        <v>7.1088</v>
       </c>
       <c r="G17">
         <v>12</v>
@@ -2669,45 +2669,45 @@
         <v>2.872333333333333</v>
       </c>
       <c r="M17">
-        <v>0.35655075</v>
+        <v>0.38600784</v>
       </c>
       <c r="N17">
-        <v>2.515782583333333</v>
+        <v>2.486325493333333</v>
       </c>
       <c r="O17">
-        <v>0.4276830391666667</v>
+        <v>0.4226753338666667</v>
       </c>
       <c r="P17">
-        <v>2.088099544166667</v>
+        <v>2.063650159466667</v>
       </c>
       <c r="Q17">
-        <v>5.299099544166666</v>
+        <v>5.274650159466667</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.08420757709110885</v>
+        <v>0.08459701109860501</v>
       </c>
       <c r="T17">
-        <v>0.8870110182704124</v>
+        <v>0.8960048752564668</v>
       </c>
       <c r="U17">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V17">
         <v>0.17</v>
       </c>
       <c r="W17">
-        <v>0.044405</v>
+        <v>0.045069</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y17">
-        <v>8.055889192024793</v>
+        <v>7.441126929788092</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2715,22 +2715,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.07827252932282822</v>
+        <v>0.07820826811821389</v>
       </c>
       <c r="C18">
-        <v>35.59371108612395</v>
+        <v>35.21029000566023</v>
       </c>
       <c r="D18">
-        <v>30.70251108612394</v>
+        <v>30.76339000566022</v>
       </c>
       <c r="E18">
-        <v>-27.69119999999999</v>
+        <v>-27.2469</v>
       </c>
       <c r="F18">
-        <v>7.1088</v>
+        <v>7.553100000000001</v>
       </c>
       <c r="G18">
         <v>12</v>
@@ -2751,28 +2751,28 @@
         <v>2.872333333333333</v>
       </c>
       <c r="M18">
-        <v>0.38600784</v>
+        <v>0.41013333</v>
       </c>
       <c r="N18">
-        <v>2.486325493333333</v>
+        <v>2.462200003333333</v>
       </c>
       <c r="O18">
-        <v>0.4226753338666667</v>
+        <v>0.4185740005666667</v>
       </c>
       <c r="P18">
-        <v>2.063650159466667</v>
+        <v>2.043626002766667</v>
       </c>
       <c r="Q18">
-        <v>5.274650159466667</v>
+        <v>5.254626002766667</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.08459701109860501</v>
+        <v>0.08499582905808903</v>
       </c>
       <c r="T18">
-        <v>0.8960048752564668</v>
+        <v>0.9052154516879682</v>
       </c>
       <c r="U18">
         <v>0.0543</v>
@@ -2789,7 +2789,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>7.441126929788092</v>
+        <v>7.003413580977028</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2797,22 +2797,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.07820826811821389</v>
+        <v>0.07814400691359956</v>
       </c>
       <c r="C19">
-        <v>35.21029000566023</v>
+        <v>34.82711083416689</v>
       </c>
       <c r="D19">
-        <v>30.76339000566022</v>
+        <v>30.82451083416688</v>
       </c>
       <c r="E19">
-        <v>-27.2469</v>
+        <v>-26.8026</v>
       </c>
       <c r="F19">
-        <v>7.553100000000001</v>
+        <v>7.997400000000001</v>
       </c>
       <c r="G19">
         <v>12</v>
@@ -2833,28 +2833,28 @@
         <v>2.872333333333333</v>
       </c>
       <c r="M19">
-        <v>0.41013333</v>
+        <v>0.43425882</v>
       </c>
       <c r="N19">
-        <v>2.462200003333333</v>
+        <v>2.438074513333333</v>
       </c>
       <c r="O19">
-        <v>0.4185740005666667</v>
+        <v>0.4144726672666667</v>
       </c>
       <c r="P19">
-        <v>2.043626002766667</v>
+        <v>2.023601846066666</v>
       </c>
       <c r="Q19">
-        <v>5.254626002766667</v>
+        <v>5.234601846066666</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.08499582905808903</v>
+        <v>0.08540437428487752</v>
       </c>
       <c r="T19">
-        <v>0.9052154516879682</v>
+        <v>0.9146506763251161</v>
       </c>
       <c r="U19">
         <v>0.0543</v>
@@ -2871,7 +2871,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>7.003413580977028</v>
+        <v>6.614335048700526</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2879,22 +2879,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.07814400691359956</v>
+        <v>0.07807974570898527</v>
       </c>
       <c r="C20">
-        <v>34.82711083416689</v>
+        <v>34.44417501639148</v>
       </c>
       <c r="D20">
-        <v>30.82451083416688</v>
+        <v>30.88587501639148</v>
       </c>
       <c r="E20">
-        <v>-26.8026</v>
+        <v>-26.3583</v>
       </c>
       <c r="F20">
-        <v>7.9974</v>
+        <v>8.441700000000001</v>
       </c>
       <c r="G20">
         <v>12</v>
@@ -2915,28 +2915,28 @@
         <v>2.872333333333333</v>
       </c>
       <c r="M20">
-        <v>0.43425882</v>
+        <v>0.4583843100000001</v>
       </c>
       <c r="N20">
-        <v>2.438074513333333</v>
+        <v>2.413949023333333</v>
       </c>
       <c r="O20">
-        <v>0.4144726672666667</v>
+        <v>0.4103713339666666</v>
       </c>
       <c r="P20">
-        <v>2.023601846066666</v>
+        <v>2.003577689366666</v>
       </c>
       <c r="Q20">
-        <v>5.234601846066666</v>
+        <v>5.214577689366666</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.08540437428487752</v>
+        <v>0.08582300704812995</v>
       </c>
       <c r="T20">
-        <v>0.9146506763251161</v>
+        <v>0.9243188694718233</v>
       </c>
       <c r="U20">
         <v>0.0543</v>
@@ -2953,7 +2953,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>6.614335048700526</v>
+        <v>6.266212151400498</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2961,22 +2961,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.07807974570898527</v>
+        <v>0.07818148450437094</v>
       </c>
       <c r="C21">
-        <v>34.44417501639148</v>
+        <v>33.90283524916968</v>
       </c>
       <c r="D21">
-        <v>30.88587501639148</v>
+        <v>30.78883524916969</v>
       </c>
       <c r="E21">
-        <v>-26.3583</v>
+        <v>-25.91399999999999</v>
       </c>
       <c r="F21">
-        <v>8.441700000000001</v>
+        <v>8.886000000000001</v>
       </c>
       <c r="G21">
         <v>12</v>
@@ -2997,45 +2997,45 @@
         <v>2.872333333333333</v>
       </c>
       <c r="M21">
-        <v>0.4583843100000001</v>
+        <v>0.4913958</v>
       </c>
       <c r="N21">
-        <v>2.413949023333333</v>
+        <v>2.380937533333333</v>
       </c>
       <c r="O21">
-        <v>0.4103713339666666</v>
+        <v>0.4047593806666667</v>
       </c>
       <c r="P21">
-        <v>2.003577689366666</v>
+        <v>1.976178152666667</v>
       </c>
       <c r="Q21">
-        <v>5.214577689366666</v>
+        <v>5.187178152666666</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.08582300704812995</v>
+        <v>0.08625210563046368</v>
       </c>
       <c r="T21">
-        <v>0.9243188694718233</v>
+        <v>0.9342287674471981</v>
       </c>
       <c r="U21">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V21">
         <v>0.17</v>
       </c>
       <c r="W21">
-        <v>0.045069</v>
+        <v>0.045899</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y21">
-        <v>6.266212151400498</v>
+        <v>5.845254137974588</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.07818148450437094</v>
+        <v>0.07812552329975664</v>
       </c>
       <c r="C22">
-        <v>33.90283524916968</v>
+        <v>33.51183617467173</v>
       </c>
       <c r="D22">
-        <v>30.78883524916969</v>
+        <v>30.84213617467173</v>
       </c>
       <c r="E22">
-        <v>-25.91399999999999</v>
+        <v>-25.4697</v>
       </c>
       <c r="F22">
-        <v>8.886000000000001</v>
+        <v>9.330300000000001</v>
       </c>
       <c r="G22">
         <v>12</v>
@@ -3079,28 +3079,28 @@
         <v>2.872333333333333</v>
       </c>
       <c r="M22">
-        <v>0.4913958</v>
+        <v>0.5159655900000001</v>
       </c>
       <c r="N22">
-        <v>2.380937533333333</v>
+        <v>2.356367743333333</v>
       </c>
       <c r="O22">
-        <v>0.4047593806666667</v>
+        <v>0.4005825163666667</v>
       </c>
       <c r="P22">
-        <v>1.976178152666667</v>
+        <v>1.955785226966666</v>
       </c>
       <c r="Q22">
-        <v>5.187178152666666</v>
+        <v>5.166785226966667</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.08625210563046368</v>
+        <v>0.08669206746804636</v>
       </c>
       <c r="T22">
-        <v>0.9342287674471981</v>
+        <v>0.9443895489156202</v>
       </c>
       <c r="U22">
         <v>0.0553</v>
@@ -3117,7 +3117,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>5.845254137974588</v>
+        <v>5.566908702832941</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3125,22 +3125,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.07812552329975662</v>
+        <v>0.07806956209514231</v>
       </c>
       <c r="C23">
-        <v>33.51183617467175</v>
+        <v>33.12102196689057</v>
       </c>
       <c r="D23">
-        <v>30.84213617467175</v>
+        <v>30.89562196689058</v>
       </c>
       <c r="E23">
-        <v>-25.4697</v>
+        <v>-25.0254</v>
       </c>
       <c r="F23">
-        <v>9.330299999999999</v>
+        <v>9.7746</v>
       </c>
       <c r="G23">
         <v>12</v>
@@ -3161,28 +3161,28 @@
         <v>2.872333333333333</v>
       </c>
       <c r="M23">
-        <v>0.51596559</v>
+        <v>0.54053538</v>
       </c>
       <c r="N23">
-        <v>2.356367743333333</v>
+        <v>2.331797953333333</v>
       </c>
       <c r="O23">
-        <v>0.4005825163666667</v>
+        <v>0.3964056520666667</v>
       </c>
       <c r="P23">
-        <v>1.955785226966666</v>
+        <v>1.935392301266667</v>
       </c>
       <c r="Q23">
-        <v>5.166785226966667</v>
+        <v>5.146392301266666</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.08669206746804636</v>
+        <v>0.08714331037838757</v>
       </c>
       <c r="T23">
-        <v>0.9443895489156202</v>
+        <v>0.9548108632422071</v>
       </c>
       <c r="U23">
         <v>0.0553</v>
@@ -3199,7 +3199,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>5.566908702832942</v>
+        <v>5.313867398158716</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3207,22 +3207,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.07806956209514231</v>
+        <v>0.07801360089052799</v>
       </c>
       <c r="C24">
-        <v>33.12102196689057</v>
+        <v>32.73039358927304</v>
       </c>
       <c r="D24">
-        <v>30.89562196689058</v>
+        <v>30.94929358927304</v>
       </c>
       <c r="E24">
-        <v>-25.0254</v>
+        <v>-24.5811</v>
       </c>
       <c r="F24">
-        <v>9.7746</v>
+        <v>10.2189</v>
       </c>
       <c r="G24">
         <v>12</v>
@@ -3243,28 +3243,28 @@
         <v>2.872333333333333</v>
       </c>
       <c r="M24">
-        <v>0.54053538</v>
+        <v>0.56510517</v>
       </c>
       <c r="N24">
-        <v>2.331797953333333</v>
+        <v>2.307228163333333</v>
       </c>
       <c r="O24">
-        <v>0.3964056520666667</v>
+        <v>0.3922287877666666</v>
       </c>
       <c r="P24">
-        <v>1.935392301266667</v>
+        <v>1.914999375566666</v>
       </c>
       <c r="Q24">
-        <v>5.146392301266666</v>
+        <v>5.125999375566666</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.08714331037838757</v>
+        <v>0.08760627388380257</v>
       </c>
       <c r="T24">
-        <v>0.9548108632422071</v>
+        <v>0.9655028610577963</v>
       </c>
       <c r="U24">
         <v>0.0553</v>
@@ -3281,7 +3281,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>5.313867398158716</v>
+        <v>5.082829685195294</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3289,22 +3289,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.07801360089052799</v>
+        <v>0.07795763968591367</v>
       </c>
       <c r="C25">
-        <v>32.73039358927304</v>
+        <v>32.33995201197241</v>
       </c>
       <c r="D25">
-        <v>30.94929358927304</v>
+        <v>31.00315201197241</v>
       </c>
       <c r="E25">
-        <v>-24.5811</v>
+        <v>-24.13679999999999</v>
       </c>
       <c r="F25">
-        <v>10.2189</v>
+        <v>10.6632</v>
       </c>
       <c r="G25">
         <v>12</v>
@@ -3325,28 +3325,28 @@
         <v>2.872333333333333</v>
       </c>
       <c r="M25">
-        <v>0.56510517</v>
+        <v>0.5896749600000001</v>
       </c>
       <c r="N25">
-        <v>2.307228163333333</v>
+        <v>2.282658373333333</v>
       </c>
       <c r="O25">
-        <v>0.3922287877666666</v>
+        <v>0.3880519234666667</v>
       </c>
       <c r="P25">
-        <v>1.914999375566666</v>
+        <v>1.894606449866667</v>
       </c>
       <c r="Q25">
-        <v>5.125999375566666</v>
+        <v>5.105606449866666</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.08760627388380257</v>
+        <v>0.08808142063936009</v>
       </c>
       <c r="T25">
-        <v>0.9655028610577963</v>
+        <v>0.9764762272369535</v>
       </c>
       <c r="U25">
         <v>0.0553</v>
@@ -3363,7 +3363,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>5.082829685195294</v>
+        <v>4.871045114978823</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3371,22 +3371,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.07795763968591367</v>
+        <v>0.07790167848129936</v>
       </c>
       <c r="C26">
-        <v>32.33995201197241</v>
+        <v>31.94969821190681</v>
       </c>
       <c r="D26">
-        <v>31.00315201197241</v>
+        <v>31.05719821190682</v>
       </c>
       <c r="E26">
-        <v>-24.1368</v>
+        <v>-23.6925</v>
       </c>
       <c r="F26">
-        <v>10.6632</v>
+        <v>11.1075</v>
       </c>
       <c r="G26">
         <v>12</v>
@@ -3407,28 +3407,28 @@
         <v>2.872333333333333</v>
       </c>
       <c r="M26">
-        <v>0.58967496</v>
+        <v>0.61424475</v>
       </c>
       <c r="N26">
-        <v>2.282658373333333</v>
+        <v>2.258088583333333</v>
       </c>
       <c r="O26">
-        <v>0.3880519234666667</v>
+        <v>0.3838750591666666</v>
       </c>
       <c r="P26">
-        <v>1.894606449866667</v>
+        <v>1.874213524166666</v>
       </c>
       <c r="Q26">
-        <v>5.105606449866666</v>
+        <v>5.085213524166666</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.08808142063936009</v>
+        <v>0.0885692379750658</v>
       </c>
       <c r="T26">
-        <v>0.9764762272369535</v>
+        <v>0.9877422165142218</v>
       </c>
       <c r="U26">
         <v>0.0553</v>
@@ -3445,7 +3445,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>4.871045114978823</v>
+        <v>4.676203310379671</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3453,22 +3453,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.07790167848129936</v>
+        <v>0.07838521727668503</v>
       </c>
       <c r="C27">
-        <v>31.94969821190681</v>
+        <v>31.04453400824278</v>
       </c>
       <c r="D27">
-        <v>31.05719821190682</v>
+        <v>30.59633400824277</v>
       </c>
       <c r="E27">
-        <v>-23.6925</v>
+        <v>-23.2482</v>
       </c>
       <c r="F27">
-        <v>11.1075</v>
+        <v>11.5518</v>
       </c>
       <c r="G27">
         <v>12</v>
@@ -3489,45 +3489,45 @@
         <v>2.872333333333333</v>
       </c>
       <c r="M27">
-        <v>0.61424475</v>
+        <v>0.6676940400000001</v>
       </c>
       <c r="N27">
-        <v>2.258088583333333</v>
+        <v>2.204639293333333</v>
       </c>
       <c r="O27">
-        <v>0.3838750591666666</v>
+        <v>0.3747886798666666</v>
       </c>
       <c r="P27">
-        <v>1.874213524166666</v>
+        <v>1.829850613466666</v>
       </c>
       <c r="Q27">
-        <v>5.085213524166666</v>
+        <v>5.040850613466667</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.0885692379750658</v>
+        <v>0.08907023956308788</v>
       </c>
       <c r="T27">
-        <v>0.9877422165142218</v>
+        <v>0.9993126919881729</v>
       </c>
       <c r="U27">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V27">
         <v>0.17</v>
       </c>
       <c r="W27">
-        <v>0.045899</v>
+        <v>0.047974</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y27">
-        <v>4.676203310379671</v>
+        <v>4.301870559355798</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3535,22 +3535,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.07838521727668503</v>
+        <v>0.07835000607207071</v>
       </c>
       <c r="C28">
-        <v>31.04453400824278</v>
+        <v>30.63333181396443</v>
       </c>
       <c r="D28">
-        <v>30.59633400824277</v>
+        <v>30.62943181396443</v>
       </c>
       <c r="E28">
-        <v>-23.2482</v>
+        <v>-22.8039</v>
       </c>
       <c r="F28">
-        <v>11.5518</v>
+        <v>11.9961</v>
       </c>
       <c r="G28">
         <v>12</v>
@@ -3571,28 +3571,28 @@
         <v>2.872333333333333</v>
       </c>
       <c r="M28">
-        <v>0.6676940400000001</v>
+        <v>0.6933745800000001</v>
       </c>
       <c r="N28">
-        <v>2.204639293333333</v>
+        <v>2.178958753333333</v>
       </c>
       <c r="O28">
-        <v>0.3747886798666666</v>
+        <v>0.3704229880666667</v>
       </c>
       <c r="P28">
-        <v>1.829850613466666</v>
+        <v>1.808535765266666</v>
       </c>
       <c r="Q28">
-        <v>5.040850613466667</v>
+        <v>5.019535765266666</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.08907023956308788</v>
+        <v>0.08958496722201467</v>
       </c>
       <c r="T28">
-        <v>0.9993126919881729</v>
+        <v>1.011200166790177</v>
       </c>
       <c r="U28">
         <v>0.0578</v>
@@ -3609,7 +3609,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>4.301870559355798</v>
+        <v>4.142542020120398</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3617,22 +3617,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.07835000607207071</v>
+        <v>0.0791281948674564</v>
       </c>
       <c r="C29">
-        <v>30.63333181396443</v>
+        <v>29.47385714754614</v>
       </c>
       <c r="D29">
-        <v>30.62943181396443</v>
+        <v>29.91425714754614</v>
       </c>
       <c r="E29">
-        <v>-22.8039</v>
+        <v>-22.3596</v>
       </c>
       <c r="F29">
-        <v>11.9961</v>
+        <v>12.4404</v>
       </c>
       <c r="G29">
         <v>12</v>
@@ -3653,45 +3653,45 @@
         <v>2.872333333333333</v>
       </c>
       <c r="M29">
-        <v>0.6933745800000001</v>
+        <v>0.76259652</v>
       </c>
       <c r="N29">
-        <v>2.178958753333333</v>
+        <v>2.109736813333333</v>
       </c>
       <c r="O29">
-        <v>0.3704229880666667</v>
+        <v>0.3586552582666666</v>
       </c>
       <c r="P29">
-        <v>1.808535765266666</v>
+        <v>1.751081555066666</v>
       </c>
       <c r="Q29">
-        <v>5.019535765266666</v>
+        <v>4.962081555066666</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.08958496722201467</v>
+        <v>0.09011399287146722</v>
       </c>
       <c r="T29">
-        <v>1.011200166790177</v>
+        <v>1.023417849225571</v>
       </c>
       <c r="U29">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V29">
         <v>0.17</v>
       </c>
       <c r="W29">
-        <v>0.047974</v>
+        <v>0.050879</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y29">
-        <v>4.142542020120398</v>
+        <v>3.766517756117393</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3699,22 +3699,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.0791281948674564</v>
+        <v>0.07912203366284208</v>
       </c>
       <c r="C30">
-        <v>29.47385714754614</v>
+        <v>29.03508825831315</v>
       </c>
       <c r="D30">
-        <v>29.91425714754614</v>
+        <v>29.91978825831315</v>
       </c>
       <c r="E30">
-        <v>-22.3596</v>
+        <v>-21.91529999999999</v>
       </c>
       <c r="F30">
-        <v>12.4404</v>
+        <v>12.8847</v>
       </c>
       <c r="G30">
         <v>12</v>
@@ -3735,28 +3735,28 @@
         <v>2.872333333333333</v>
       </c>
       <c r="M30">
-        <v>0.76259652</v>
+        <v>0.7898321100000002</v>
       </c>
       <c r="N30">
-        <v>2.109736813333333</v>
+        <v>2.082501223333333</v>
       </c>
       <c r="O30">
-        <v>0.3586552582666666</v>
+        <v>0.3540252079666666</v>
       </c>
       <c r="P30">
-        <v>1.751081555066666</v>
+        <v>1.728476015366666</v>
       </c>
       <c r="Q30">
-        <v>4.962081555066666</v>
+        <v>4.939476015366666</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.09011399287146722</v>
+        <v>0.09065792065189027</v>
       </c>
       <c r="T30">
-        <v>1.023417849225571</v>
+        <v>1.035979691729567</v>
       </c>
       <c r="U30">
         <v>0.0613</v>
@@ -3773,7 +3773,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>3.766517756117393</v>
+        <v>3.636637833492655</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3781,22 +3781,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.07912203366284208</v>
+        <v>0.07911587245822777</v>
       </c>
       <c r="C31">
-        <v>29.03508825831315</v>
+        <v>28.5963214148501</v>
       </c>
       <c r="D31">
-        <v>29.91978825831315</v>
+        <v>29.92532141485011</v>
       </c>
       <c r="E31">
-        <v>-21.9153</v>
+        <v>-21.471</v>
       </c>
       <c r="F31">
-        <v>12.8847</v>
+        <v>13.329</v>
       </c>
       <c r="G31">
         <v>12</v>
@@ -3817,28 +3817,28 @@
         <v>2.872333333333333</v>
       </c>
       <c r="M31">
-        <v>0.78983211</v>
+        <v>0.8170677</v>
       </c>
       <c r="N31">
-        <v>2.082501223333333</v>
+        <v>2.055265633333333</v>
       </c>
       <c r="O31">
-        <v>0.3540252079666667</v>
+        <v>0.3493951576666667</v>
       </c>
       <c r="P31">
-        <v>1.728476015366667</v>
+        <v>1.705870475666666</v>
       </c>
       <c r="Q31">
-        <v>4.939476015366667</v>
+        <v>4.916870475666666</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.09065792065189027</v>
+        <v>0.09121738922603966</v>
       </c>
       <c r="T31">
-        <v>1.035979691729567</v>
+        <v>1.048900444019392</v>
       </c>
       <c r="U31">
         <v>0.0613</v>
@@ -3855,7 +3855,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>3.636637833492656</v>
+        <v>3.515416572376235</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3863,22 +3863,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.07911587245822777</v>
+        <v>0.07983015125361345</v>
       </c>
       <c r="C32">
-        <v>28.5963214148501</v>
+        <v>27.52390129947275</v>
       </c>
       <c r="D32">
-        <v>29.92532141485011</v>
+        <v>29.29720129947275</v>
       </c>
       <c r="E32">
-        <v>-21.471</v>
+        <v>-21.0267</v>
       </c>
       <c r="F32">
-        <v>13.329</v>
+        <v>13.7733</v>
       </c>
       <c r="G32">
         <v>12</v>
@@ -3899,45 +3899,45 @@
         <v>2.872333333333333</v>
       </c>
       <c r="M32">
-        <v>0.8170677</v>
+        <v>0.88286853</v>
       </c>
       <c r="N32">
-        <v>2.055265633333333</v>
+        <v>1.989464803333333</v>
       </c>
       <c r="O32">
-        <v>0.3493951576666667</v>
+        <v>0.3382090165666666</v>
       </c>
       <c r="P32">
-        <v>1.705870475666666</v>
+        <v>1.651255786766666</v>
       </c>
       <c r="Q32">
-        <v>4.916870475666666</v>
+        <v>4.862255786766666</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.09121738922603966</v>
+        <v>0.0917930742805992</v>
       </c>
       <c r="T32">
-        <v>1.048900444019392</v>
+        <v>1.062195710868342</v>
       </c>
       <c r="U32">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V32">
         <v>0.17</v>
       </c>
       <c r="W32">
-        <v>0.050879</v>
+        <v>0.053203</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y32">
-        <v>3.515416572376235</v>
+        <v>3.25341003301288</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3945,22 +3945,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.07983015125361345</v>
+        <v>0.07984723004899913</v>
       </c>
       <c r="C33">
-        <v>27.52390129947275</v>
+        <v>27.06490521683557</v>
       </c>
       <c r="D33">
-        <v>29.29720129947275</v>
+        <v>29.28250521683558</v>
       </c>
       <c r="E33">
-        <v>-21.0267</v>
+        <v>-20.5824</v>
       </c>
       <c r="F33">
-        <v>13.7733</v>
+        <v>14.2176</v>
       </c>
       <c r="G33">
         <v>12</v>
@@ -3981,28 +3981,28 @@
         <v>2.872333333333333</v>
       </c>
       <c r="M33">
-        <v>0.88286853</v>
+        <v>0.9113481600000001</v>
       </c>
       <c r="N33">
-        <v>1.989464803333333</v>
+        <v>1.960985173333333</v>
       </c>
       <c r="O33">
-        <v>0.3382090165666666</v>
+        <v>0.3333674794666666</v>
       </c>
       <c r="P33">
-        <v>1.651255786766666</v>
+        <v>1.627617693866666</v>
       </c>
       <c r="Q33">
-        <v>4.862255786766666</v>
+        <v>4.838617693866667</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.0917930742805992</v>
+        <v>0.09238569124852813</v>
       </c>
       <c r="T33">
-        <v>1.062195710868342</v>
+        <v>1.075882014977555</v>
       </c>
       <c r="U33">
         <v>0.0641</v>
@@ -4019,7 +4019,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>3.25341003301288</v>
+        <v>3.151740969481228</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4027,22 +4027,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.07984723004899913</v>
+        <v>0.07986430884438481</v>
       </c>
       <c r="C34">
-        <v>27.06490521683557</v>
+        <v>26.6059238705249</v>
       </c>
       <c r="D34">
-        <v>29.28250521683558</v>
+        <v>29.2678238705249</v>
       </c>
       <c r="E34">
-        <v>-20.5824</v>
+        <v>-20.13809999999999</v>
       </c>
       <c r="F34">
-        <v>14.2176</v>
+        <v>14.6619</v>
       </c>
       <c r="G34">
         <v>12</v>
@@ -4063,28 +4063,28 @@
         <v>2.872333333333333</v>
       </c>
       <c r="M34">
-        <v>0.9113481600000001</v>
+        <v>0.9398277900000002</v>
       </c>
       <c r="N34">
-        <v>1.960985173333333</v>
+        <v>1.932505543333333</v>
       </c>
       <c r="O34">
-        <v>0.3333674794666666</v>
+        <v>0.3285259423666666</v>
       </c>
       <c r="P34">
-        <v>1.627617693866666</v>
+        <v>1.603979600966666</v>
       </c>
       <c r="Q34">
-        <v>4.838617693866667</v>
+        <v>4.814979600966666</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.09238569124852813</v>
+        <v>0.09299599827520122</v>
       </c>
       <c r="T34">
-        <v>1.075882014977555</v>
+        <v>1.089976865478088</v>
       </c>
       <c r="U34">
         <v>0.0641</v>
@@ -4101,7 +4101,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>3.151740969481228</v>
+        <v>3.056233667375735</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.07986430884438481</v>
+        <v>0.08208254763977049</v>
       </c>
       <c r="C35">
-        <v>26.6059238705249</v>
+        <v>24.37225056050548</v>
       </c>
       <c r="D35">
-        <v>29.2678238705249</v>
+        <v>27.47845056050548</v>
       </c>
       <c r="E35">
-        <v>-20.13809999999999</v>
+        <v>-19.6938</v>
       </c>
       <c r="F35">
-        <v>14.6619</v>
+        <v>15.1062</v>
       </c>
       <c r="G35">
         <v>12</v>
@@ -4145,45 +4145,45 @@
         <v>2.872333333333333</v>
       </c>
       <c r="M35">
-        <v>0.9398277900000002</v>
+        <v>1.08613578</v>
       </c>
       <c r="N35">
-        <v>1.932505543333333</v>
+        <v>1.786197553333333</v>
       </c>
       <c r="O35">
-        <v>0.3285259423666666</v>
+        <v>0.3036535840666666</v>
       </c>
       <c r="P35">
-        <v>1.603979600966666</v>
+        <v>1.482543969266666</v>
       </c>
       <c r="Q35">
-        <v>4.814979600966666</v>
+        <v>4.693543969266666</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.09299599827520122</v>
+        <v>0.09362479945419772</v>
       </c>
       <c r="T35">
-        <v>1.089976865478088</v>
+        <v>1.104498832660455</v>
       </c>
       <c r="U35">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V35">
         <v>0.17</v>
       </c>
       <c r="W35">
-        <v>0.053203</v>
+        <v>0.059677</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y35">
-        <v>3.056233667375735</v>
+        <v>2.644543514930825</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4191,22 +4191,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08208254763977049</v>
+        <v>0.08216436643515618</v>
       </c>
       <c r="C36">
-        <v>24.37225056050548</v>
+        <v>23.86612482437077</v>
       </c>
       <c r="D36">
-        <v>27.47845056050548</v>
+        <v>27.41662482437077</v>
       </c>
       <c r="E36">
-        <v>-19.6938</v>
+        <v>-19.2495</v>
       </c>
       <c r="F36">
-        <v>15.1062</v>
+        <v>15.5505</v>
       </c>
       <c r="G36">
         <v>12</v>
@@ -4227,28 +4227,28 @@
         <v>2.872333333333333</v>
       </c>
       <c r="M36">
-        <v>1.08613578</v>
+        <v>1.11808095</v>
       </c>
       <c r="N36">
-        <v>1.786197553333333</v>
+        <v>1.754252383333333</v>
       </c>
       <c r="O36">
-        <v>0.3036535840666666</v>
+        <v>0.2982229051666666</v>
       </c>
       <c r="P36">
-        <v>1.482543969266666</v>
+        <v>1.456029478166666</v>
       </c>
       <c r="Q36">
-        <v>4.693543969266666</v>
+        <v>4.667029478166667</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.09362479945419772</v>
+        <v>0.09427294836177874</v>
       </c>
       <c r="T36">
-        <v>1.104498832660455</v>
+        <v>1.11946762960228</v>
       </c>
       <c r="U36">
         <v>0.07190000000000001</v>
@@ -4265,7 +4265,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>2.644543514930825</v>
+        <v>2.568985128789944</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4273,22 +4273,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08216436643515618</v>
+        <v>0.08341150523054186</v>
       </c>
       <c r="C37">
-        <v>23.86612482437077</v>
+        <v>22.51273234728369</v>
       </c>
       <c r="D37">
-        <v>27.41662482437077</v>
+        <v>26.50753234728369</v>
       </c>
       <c r="E37">
-        <v>-19.2495</v>
+        <v>-18.8052</v>
       </c>
       <c r="F37">
-        <v>15.5505</v>
+        <v>15.9948</v>
       </c>
       <c r="G37">
         <v>12</v>
@@ -4309,45 +4309,45 @@
         <v>2.872333333333333</v>
       </c>
       <c r="M37">
-        <v>1.11808095</v>
+        <v>1.21240584</v>
       </c>
       <c r="N37">
-        <v>1.754252383333333</v>
+        <v>1.659927493333333</v>
       </c>
       <c r="O37">
-        <v>0.2982229051666666</v>
+        <v>0.2821876738666667</v>
       </c>
       <c r="P37">
-        <v>1.456029478166666</v>
+        <v>1.377739819466666</v>
       </c>
       <c r="Q37">
-        <v>4.667029478166667</v>
+        <v>4.588739819466666</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.09427294836177874</v>
+        <v>0.09494135192272166</v>
       </c>
       <c r="T37">
-        <v>1.11946762960228</v>
+        <v>1.134904201448537</v>
       </c>
       <c r="U37">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V37">
         <v>0.17</v>
       </c>
       <c r="W37">
-        <v>0.059677</v>
+        <v>0.062914</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y37">
-        <v>2.568985128789944</v>
+        <v>2.369118688287853</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4355,22 +4355,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08341150523054186</v>
+        <v>0.08352569402592754</v>
       </c>
       <c r="C38">
-        <v>22.51273234728369</v>
+        <v>21.98819888132537</v>
       </c>
       <c r="D38">
-        <v>26.50753234728369</v>
+        <v>26.42729888132537</v>
       </c>
       <c r="E38">
-        <v>-18.8052</v>
+        <v>-18.3609</v>
       </c>
       <c r="F38">
-        <v>15.9948</v>
+        <v>16.4391</v>
       </c>
       <c r="G38">
         <v>12</v>
@@ -4391,28 +4391,28 @@
         <v>2.872333333333333</v>
       </c>
       <c r="M38">
-        <v>1.21240584</v>
+        <v>1.24608378</v>
       </c>
       <c r="N38">
-        <v>1.659927493333333</v>
+        <v>1.626249553333333</v>
       </c>
       <c r="O38">
-        <v>0.2821876738666667</v>
+        <v>0.2764624240666666</v>
       </c>
       <c r="P38">
-        <v>1.377739819466666</v>
+        <v>1.349787129266666</v>
       </c>
       <c r="Q38">
-        <v>4.588739819466666</v>
+        <v>4.560787129266666</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.09494135192272166</v>
+        <v>0.09563097464432943</v>
       </c>
       <c r="T38">
-        <v>1.134904201448537</v>
+        <v>1.150830823194675</v>
       </c>
       <c r="U38">
         <v>0.07580000000000001</v>
@@ -4429,7 +4429,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>2.369118688287853</v>
+        <v>2.305088453469263</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4437,22 +4437,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08352569402592754</v>
+        <v>0.08363988282131322</v>
       </c>
       <c r="C39">
-        <v>21.98819888132537</v>
+        <v>21.46414965380249</v>
       </c>
       <c r="D39">
-        <v>26.42729888132537</v>
+        <v>26.34754965380249</v>
       </c>
       <c r="E39">
-        <v>-18.3609</v>
+        <v>-17.9166</v>
       </c>
       <c r="F39">
-        <v>16.4391</v>
+        <v>16.8834</v>
       </c>
       <c r="G39">
         <v>12</v>
@@ -4473,28 +4473,28 @@
         <v>2.872333333333333</v>
       </c>
       <c r="M39">
-        <v>1.24608378</v>
+        <v>1.27976172</v>
       </c>
       <c r="N39">
-        <v>1.626249553333333</v>
+        <v>1.592571613333333</v>
       </c>
       <c r="O39">
-        <v>0.2764624240666666</v>
+        <v>0.2707371742666666</v>
       </c>
       <c r="P39">
-        <v>1.349787129266666</v>
+        <v>1.321834439066666</v>
       </c>
       <c r="Q39">
-        <v>4.560787129266666</v>
+        <v>4.532834439066666</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.09563097464432943</v>
+        <v>0.09634284326018262</v>
       </c>
       <c r="T39">
-        <v>1.150830823194675</v>
+        <v>1.167271206932624</v>
       </c>
       <c r="U39">
         <v>0.07580000000000001</v>
@@ -4511,7 +4511,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>2.305088453469263</v>
+        <v>2.244428231009545</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4519,22 +4519,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08363988282131322</v>
+        <v>0.0837540716166989</v>
       </c>
       <c r="C40">
-        <v>21.46414965380249</v>
+        <v>20.94058029406907</v>
       </c>
       <c r="D40">
-        <v>26.34754965380249</v>
+        <v>26.26828029406908</v>
       </c>
       <c r="E40">
-        <v>-17.9166</v>
+        <v>-17.4723</v>
       </c>
       <c r="F40">
-        <v>16.8834</v>
+        <v>17.3277</v>
       </c>
       <c r="G40">
         <v>12</v>
@@ -4555,28 +4555,28 @@
         <v>2.872333333333333</v>
       </c>
       <c r="M40">
-        <v>1.27976172</v>
+        <v>1.31343966</v>
       </c>
       <c r="N40">
-        <v>1.592571613333333</v>
+        <v>1.558893673333333</v>
       </c>
       <c r="O40">
-        <v>0.2707371742666666</v>
+        <v>0.2650119244666667</v>
       </c>
       <c r="P40">
-        <v>1.321834439066666</v>
+        <v>1.293881748866667</v>
       </c>
       <c r="Q40">
-        <v>4.532834439066666</v>
+        <v>4.504881748866667</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.09634284326018262</v>
+        <v>0.09707805183065393</v>
       </c>
       <c r="T40">
-        <v>1.167271206932624</v>
+        <v>1.184250619645588</v>
       </c>
       <c r="U40">
         <v>0.07580000000000001</v>
@@ -4593,7 +4593,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>2.244428231009545</v>
+        <v>2.186878789188788</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4601,22 +4601,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.0837540716166989</v>
+        <v>0.08386826041208459</v>
       </c>
       <c r="C41">
-        <v>20.94058029406907</v>
+        <v>20.41748648391952</v>
       </c>
       <c r="D41">
-        <v>26.26828029406908</v>
+        <v>26.18948648391952</v>
       </c>
       <c r="E41">
-        <v>-17.4723</v>
+        <v>-17.028</v>
       </c>
       <c r="F41">
-        <v>17.3277</v>
+        <v>17.772</v>
       </c>
       <c r="G41">
         <v>12</v>
@@ -4637,28 +4637,28 @@
         <v>2.872333333333333</v>
       </c>
       <c r="M41">
-        <v>1.31343966</v>
+        <v>1.3471176</v>
       </c>
       <c r="N41">
-        <v>1.558893673333333</v>
+        <v>1.525215733333333</v>
       </c>
       <c r="O41">
-        <v>0.2650119244666667</v>
+        <v>0.2592866746666666</v>
       </c>
       <c r="P41">
-        <v>1.293881748866667</v>
+        <v>1.265929058666666</v>
       </c>
       <c r="Q41">
-        <v>4.504881748866667</v>
+        <v>4.476929058666666</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.09707805183065393</v>
+        <v>0.09783776735347433</v>
       </c>
       <c r="T41">
-        <v>1.184250619645588</v>
+        <v>1.201796012782317</v>
       </c>
       <c r="U41">
         <v>0.07580000000000001</v>
@@ -4675,7 +4675,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>2.186878789188788</v>
+        <v>2.132206819459068</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4683,22 +4683,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.08386826041208459</v>
+        <v>0.08398244920747026</v>
       </c>
       <c r="C42">
-        <v>20.41748648391952</v>
+        <v>19.89486395680455</v>
       </c>
       <c r="D42">
-        <v>26.18948648391952</v>
+        <v>26.11116395680455</v>
       </c>
       <c r="E42">
-        <v>-17.028</v>
+        <v>-16.5837</v>
       </c>
       <c r="F42">
-        <v>17.772</v>
+        <v>18.2163</v>
       </c>
       <c r="G42">
         <v>12</v>
@@ -4719,28 +4719,28 @@
         <v>2.872333333333333</v>
       </c>
       <c r="M42">
-        <v>1.3471176</v>
+        <v>1.38079554</v>
       </c>
       <c r="N42">
-        <v>1.525215733333333</v>
+        <v>1.491537793333333</v>
       </c>
       <c r="O42">
-        <v>0.2592866746666666</v>
+        <v>0.2535614248666667</v>
       </c>
       <c r="P42">
-        <v>1.265929058666666</v>
+        <v>1.237976368466666</v>
       </c>
       <c r="Q42">
-        <v>4.476929058666666</v>
+        <v>4.448976368466666</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.09783776735347433</v>
+        <v>0.09862323594486487</v>
       </c>
       <c r="T42">
-        <v>1.201796012782317</v>
+        <v>1.219936165008427</v>
       </c>
       <c r="U42">
         <v>0.07580000000000001</v>
@@ -4757,7 +4757,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>2.132206819459068</v>
+        <v>2.080201775082018</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4765,22 +4765,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.08398244920747026</v>
+        <v>0.08409663800285595</v>
       </c>
       <c r="C43">
-        <v>19.89486395680455</v>
+        <v>19.37270849706097</v>
       </c>
       <c r="D43">
-        <v>26.11116395680455</v>
+        <v>26.03330849706097</v>
       </c>
       <c r="E43">
-        <v>-16.5837</v>
+        <v>-16.13939999999999</v>
       </c>
       <c r="F43">
-        <v>18.2163</v>
+        <v>18.6606</v>
       </c>
       <c r="G43">
         <v>12</v>
@@ -4801,28 +4801,28 @@
         <v>2.872333333333333</v>
       </c>
       <c r="M43">
-        <v>1.38079554</v>
+        <v>1.41447348</v>
       </c>
       <c r="N43">
-        <v>1.491537793333333</v>
+        <v>1.457859853333333</v>
       </c>
       <c r="O43">
-        <v>0.2535614248666667</v>
+        <v>0.2478361750666666</v>
       </c>
       <c r="P43">
-        <v>1.237976368466666</v>
+        <v>1.210023678266666</v>
       </c>
       <c r="Q43">
-        <v>4.448976368466666</v>
+        <v>4.421023678266666</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.09862323594486487</v>
+        <v>0.09943578966009647</v>
       </c>
       <c r="T43">
-        <v>1.219936165008427</v>
+        <v>1.238701839725092</v>
       </c>
       <c r="U43">
         <v>0.07580000000000001</v>
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>2.080201775082018</v>
+        <v>2.030673161389588</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4847,22 +4847,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.08409663800285597</v>
+        <v>0.08927880679824164</v>
       </c>
       <c r="C44">
-        <v>19.37270849706097</v>
+        <v>15.8255404823027</v>
       </c>
       <c r="D44">
-        <v>26.03330849706096</v>
+        <v>22.9304404823027</v>
       </c>
       <c r="E44">
-        <v>-16.1394</v>
+        <v>-15.6951</v>
       </c>
       <c r="F44">
-        <v>18.6606</v>
+        <v>19.1049</v>
       </c>
       <c r="G44">
         <v>12</v>
@@ -4883,45 +4883,45 @@
         <v>2.872333333333333</v>
       </c>
       <c r="M44">
-        <v>1.41447348</v>
+        <v>1.719441</v>
       </c>
       <c r="N44">
-        <v>1.457859853333333</v>
+        <v>1.152892333333333</v>
       </c>
       <c r="O44">
-        <v>0.2478361750666666</v>
+        <v>0.1959916966666667</v>
       </c>
       <c r="P44">
-        <v>1.210023678266666</v>
+        <v>0.9569006366666666</v>
       </c>
       <c r="Q44">
-        <v>4.421023678266666</v>
+        <v>4.167900636666666</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.09943578966009647</v>
+        <v>0.1002768540320029</v>
       </c>
       <c r="T44">
-        <v>1.238701839725092</v>
+        <v>1.258125959168658</v>
       </c>
       <c r="U44">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V44">
         <v>0.17</v>
       </c>
       <c r="W44">
-        <v>0.062914</v>
+        <v>0.07469999999999999</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y44">
-        <v>2.030673161389589</v>
+        <v>1.670504154160179</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4929,22 +4929,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.08927880679824164</v>
+        <v>0.08951085559362733</v>
       </c>
       <c r="C45">
-        <v>15.8255404823027</v>
+        <v>15.25950914075565</v>
       </c>
       <c r="D45">
-        <v>22.9304404823027</v>
+        <v>22.80870914075566</v>
       </c>
       <c r="E45">
-        <v>-15.6951</v>
+        <v>-15.2508</v>
       </c>
       <c r="F45">
-        <v>19.1049</v>
+        <v>19.5492</v>
       </c>
       <c r="G45">
         <v>12</v>
@@ -4965,28 +4965,28 @@
         <v>2.872333333333333</v>
       </c>
       <c r="M45">
-        <v>1.719441</v>
+        <v>1.759428</v>
       </c>
       <c r="N45">
-        <v>1.152892333333333</v>
+        <v>1.112905333333333</v>
       </c>
       <c r="O45">
-        <v>0.1959916966666667</v>
+        <v>0.1891939066666667</v>
       </c>
       <c r="P45">
-        <v>0.9569006366666666</v>
+        <v>0.9237114266666667</v>
       </c>
       <c r="Q45">
-        <v>4.167900636666666</v>
+        <v>4.134711426666667</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1002768540320029</v>
+        <v>0.1011479564171917</v>
       </c>
       <c r="T45">
-        <v>1.258125959168658</v>
+        <v>1.278243797163779</v>
       </c>
       <c r="U45">
         <v>0.09</v>
@@ -5003,7 +5003,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>1.670504154160179</v>
+        <v>1.632538150656539</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5011,22 +5011,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.08951085559362733</v>
+        <v>0.089742904389013</v>
       </c>
       <c r="C46">
-        <v>15.25950914075565</v>
+        <v>14.69476344983</v>
       </c>
       <c r="D46">
-        <v>22.80870914075566</v>
+        <v>22.68826344983001</v>
       </c>
       <c r="E46">
-        <v>-15.2508</v>
+        <v>-14.8065</v>
       </c>
       <c r="F46">
-        <v>19.5492</v>
+        <v>19.9935</v>
       </c>
       <c r="G46">
         <v>12</v>
@@ -5047,28 +5047,28 @@
         <v>2.872333333333333</v>
       </c>
       <c r="M46">
-        <v>1.759428</v>
+        <v>1.799415</v>
       </c>
       <c r="N46">
-        <v>1.112905333333333</v>
+        <v>1.072918333333333</v>
       </c>
       <c r="O46">
-        <v>0.1891939066666667</v>
+        <v>0.1823961166666667</v>
       </c>
       <c r="P46">
-        <v>0.9237114266666667</v>
+        <v>0.8905222166666665</v>
       </c>
       <c r="Q46">
-        <v>4.134711426666667</v>
+        <v>4.101522216666666</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1011479564171917</v>
+        <v>0.1020507352527509</v>
       </c>
       <c r="T46">
-        <v>1.278243797163779</v>
+        <v>1.299093192904178</v>
       </c>
       <c r="U46">
         <v>0.09</v>
@@ -5085,7 +5085,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>1.632538150656539</v>
+        <v>1.596259525086394</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5093,22 +5093,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.089742904389013</v>
+        <v>0.08997495318439869</v>
       </c>
       <c r="C47">
-        <v>14.69476344983</v>
+        <v>14.13128314915262</v>
       </c>
       <c r="D47">
-        <v>22.68826344983001</v>
+        <v>22.56908314915261</v>
       </c>
       <c r="E47">
-        <v>-14.8065</v>
+        <v>-14.3622</v>
       </c>
       <c r="F47">
-        <v>19.9935</v>
+        <v>20.4378</v>
       </c>
       <c r="G47">
         <v>12</v>
@@ -5129,28 +5129,28 @@
         <v>2.872333333333333</v>
       </c>
       <c r="M47">
-        <v>1.799415</v>
+        <v>1.839402</v>
       </c>
       <c r="N47">
-        <v>1.072918333333333</v>
+        <v>1.032931333333333</v>
       </c>
       <c r="O47">
-        <v>0.1823961166666667</v>
+        <v>0.1755983266666667</v>
       </c>
       <c r="P47">
-        <v>0.8905222166666665</v>
+        <v>0.8573330066666667</v>
       </c>
       <c r="Q47">
-        <v>4.101522216666666</v>
+        <v>4.068333006666666</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1020507352527509</v>
+        <v>0.1029869503414791</v>
       </c>
       <c r="T47">
-        <v>1.299093192904178</v>
+        <v>1.320714788486814</v>
       </c>
       <c r="U47">
         <v>0.09</v>
@@ -5167,7 +5167,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>1.596259525086394</v>
+        <v>1.561558231062777</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.08997495318439869</v>
+        <v>0.09020700197978437</v>
       </c>
       <c r="C48">
-        <v>14.13128314915262</v>
+        <v>13.56904840183271</v>
       </c>
       <c r="D48">
-        <v>22.56908314915261</v>
+        <v>22.45114840183271</v>
       </c>
       <c r="E48">
-        <v>-14.3622</v>
+        <v>-13.9179</v>
       </c>
       <c r="F48">
-        <v>20.4378</v>
+        <v>20.8821</v>
       </c>
       <c r="G48">
         <v>12</v>
@@ -5211,28 +5211,28 @@
         <v>2.872333333333333</v>
       </c>
       <c r="M48">
-        <v>1.839402</v>
+        <v>1.879389</v>
       </c>
       <c r="N48">
-        <v>1.032931333333333</v>
+        <v>0.9929443333333332</v>
       </c>
       <c r="O48">
-        <v>0.1755983266666667</v>
+        <v>0.1688005366666667</v>
       </c>
       <c r="P48">
-        <v>0.8573330066666667</v>
+        <v>0.8241437966666665</v>
       </c>
       <c r="Q48">
-        <v>4.068333006666666</v>
+        <v>4.035143796666667</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1029869503414791</v>
+        <v>0.1039584943014799</v>
       </c>
       <c r="T48">
-        <v>1.320714788486814</v>
+        <v>1.343152293336719</v>
       </c>
       <c r="U48">
         <v>0.09</v>
@@ -5249,7 +5249,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>1.561558231062777</v>
+        <v>1.528333587848675</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5257,22 +5257,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.09020700197978437</v>
+        <v>0.1142824164226736</v>
       </c>
       <c r="C49">
-        <v>13.56904840183271</v>
+        <v>5.231909177865514</v>
       </c>
       <c r="D49">
-        <v>22.45114840183271</v>
+        <v>14.55830917786552</v>
       </c>
       <c r="E49">
-        <v>-13.9179</v>
+        <v>-13.47359999999999</v>
       </c>
       <c r="F49">
-        <v>20.8821</v>
+        <v>21.3264</v>
       </c>
       <c r="G49">
         <v>12</v>
@@ -5293,45 +5293,45 @@
         <v>2.872333333333333</v>
       </c>
       <c r="M49">
-        <v>1.879389</v>
+        <v>3.130715520000001</v>
       </c>
       <c r="N49">
-        <v>0.9929443333333332</v>
+        <v>-0.2583821866666676</v>
       </c>
       <c r="O49">
-        <v>0.1688005366666667</v>
+        <v>-0.04392497173333349</v>
       </c>
       <c r="P49">
-        <v>0.8241437966666665</v>
+        <v>-0.2144572149333341</v>
       </c>
       <c r="Q49">
-        <v>4.035143796666667</v>
+        <v>2.996542785066666</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1039584943014799</v>
+        <v>0.1054012754863336</v>
       </c>
       <c r="T49">
-        <v>1.343152293336719</v>
+        <v>1.376472874973061</v>
       </c>
       <c r="U49">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V49">
-        <v>0.17</v>
+        <v>0.1559696700473975</v>
       </c>
       <c r="W49">
-        <v>0.07469999999999999</v>
+        <v>0.123903652437042</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y49">
-        <v>1.528333587848675</v>
+        <v>0.9174686473376324</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5339,22 +5339,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1142824164226736</v>
+        <v>0.1152924164226736</v>
       </c>
       <c r="C50">
-        <v>5.231909177865525</v>
+        <v>4.576019294730497</v>
       </c>
       <c r="D50">
-        <v>14.55830917786552</v>
+        <v>14.34671929473049</v>
       </c>
       <c r="E50">
-        <v>-13.4736</v>
+        <v>-13.0293</v>
       </c>
       <c r="F50">
-        <v>21.3264</v>
+        <v>21.7707</v>
       </c>
       <c r="G50">
         <v>12</v>
@@ -5375,37 +5375,37 @@
         <v>2.872333333333333</v>
       </c>
       <c r="M50">
-        <v>3.13071552</v>
+        <v>3.19593876</v>
       </c>
       <c r="N50">
-        <v>-0.2583821866666671</v>
+        <v>-0.323605426666667</v>
       </c>
       <c r="O50">
-        <v>-0.04392497173333341</v>
+        <v>-0.0550129225333334</v>
       </c>
       <c r="P50">
-        <v>-0.2144572149333337</v>
+        <v>-0.2685925041333336</v>
       </c>
       <c r="Q50">
-        <v>2.996542785066666</v>
+        <v>2.942407495866666</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1054012754863336</v>
+        <v>0.1065699279468499</v>
       </c>
       <c r="T50">
-        <v>1.376472874973061</v>
+        <v>1.40346253918822</v>
       </c>
       <c r="U50">
         <v>0.1468</v>
       </c>
       <c r="V50">
-        <v>0.1559696700473975</v>
+        <v>0.1527866155566343</v>
       </c>
       <c r="W50">
-        <v>0.123903652437042</v>
+        <v>0.1243709248362861</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.9174686473376326</v>
+        <v>0.8987447973919667</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5421,22 +5421,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1152924164226736</v>
+        <v>0.1163024164226736</v>
       </c>
       <c r="C51">
-        <v>4.576019294730497</v>
+        <v>3.926191779179725</v>
       </c>
       <c r="D51">
-        <v>14.34671929473049</v>
+        <v>14.14119177917972</v>
       </c>
       <c r="E51">
-        <v>-13.0293</v>
+        <v>-12.585</v>
       </c>
       <c r="F51">
-        <v>21.7707</v>
+        <v>22.215</v>
       </c>
       <c r="G51">
         <v>12</v>
@@ -5457,37 +5457,37 @@
         <v>2.872333333333333</v>
       </c>
       <c r="M51">
-        <v>3.19593876</v>
+        <v>3.261162</v>
       </c>
       <c r="N51">
-        <v>-0.323605426666667</v>
+        <v>-0.3888286666666669</v>
       </c>
       <c r="O51">
-        <v>-0.0550129225333334</v>
+        <v>-0.06610087333333338</v>
       </c>
       <c r="P51">
-        <v>-0.2685925041333336</v>
+        <v>-0.3227277933333336</v>
       </c>
       <c r="Q51">
-        <v>2.942407495866666</v>
+        <v>2.888272206666666</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1065699279468499</v>
+        <v>0.1077853265057869</v>
       </c>
       <c r="T51">
-        <v>1.40346253918822</v>
+        <v>1.431531789971984</v>
       </c>
       <c r="U51">
         <v>0.1468</v>
       </c>
       <c r="V51">
-        <v>0.1527866155566343</v>
+        <v>0.1497308832455017</v>
       </c>
       <c r="W51">
-        <v>0.1243709248362861</v>
+        <v>0.1248195063395604</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5495,7 +5495,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.8987447973919667</v>
+        <v>0.8807699014441273</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5503,22 +5503,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1163024164226736</v>
+        <v>0.1173124164226736</v>
       </c>
       <c r="C52">
-        <v>3.926191779179725</v>
+        <v>3.282169767095073</v>
       </c>
       <c r="D52">
-        <v>14.14119177917972</v>
+        <v>13.94146976709508</v>
       </c>
       <c r="E52">
-        <v>-12.585</v>
+        <v>-12.1407</v>
       </c>
       <c r="F52">
-        <v>22.215</v>
+        <v>22.6593</v>
       </c>
       <c r="G52">
         <v>12</v>
@@ -5539,37 +5539,37 @@
         <v>2.872333333333333</v>
       </c>
       <c r="M52">
-        <v>3.261162</v>
+        <v>3.32638524</v>
       </c>
       <c r="N52">
-        <v>-0.3888286666666669</v>
+        <v>-0.4540519066666673</v>
       </c>
       <c r="O52">
-        <v>-0.06610087333333338</v>
+        <v>-0.07718882413333344</v>
       </c>
       <c r="P52">
-        <v>-0.3227277933333336</v>
+        <v>-0.3768630825333338</v>
       </c>
       <c r="Q52">
-        <v>2.888272206666666</v>
+        <v>2.834136917466666</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1077853265057869</v>
+        <v>0.1090503331691703</v>
       </c>
       <c r="T52">
-        <v>1.431531789971984</v>
+        <v>1.460746724461208</v>
       </c>
       <c r="U52">
         <v>0.1468</v>
       </c>
       <c r="V52">
-        <v>0.1497308832455017</v>
+        <v>0.1467949835740212</v>
       </c>
       <c r="W52">
-        <v>0.1248195063395604</v>
+        <v>0.1252504964113337</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5577,7 +5577,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.8807699014441273</v>
+        <v>0.8634999033765953</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5585,22 +5585,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1173124164226736</v>
+        <v>0.1183224164226737</v>
       </c>
       <c r="C53">
-        <v>3.282169767095073</v>
+        <v>2.643710703465697</v>
       </c>
       <c r="D53">
-        <v>13.94146976709508</v>
+        <v>13.7473107034657</v>
       </c>
       <c r="E53">
-        <v>-12.1407</v>
+        <v>-11.6964</v>
       </c>
       <c r="F53">
-        <v>22.6593</v>
+        <v>23.1036</v>
       </c>
       <c r="G53">
         <v>12</v>
@@ -5621,37 +5621,37 @@
         <v>2.872333333333333</v>
       </c>
       <c r="M53">
-        <v>3.32638524</v>
+        <v>3.39160848</v>
       </c>
       <c r="N53">
-        <v>-0.4540519066666673</v>
+        <v>-0.5192751466666672</v>
       </c>
       <c r="O53">
-        <v>-0.07718882413333344</v>
+        <v>-0.08827677493333343</v>
       </c>
       <c r="P53">
-        <v>-0.3768630825333338</v>
+        <v>-0.4309983717333338</v>
       </c>
       <c r="Q53">
-        <v>2.834136917466666</v>
+        <v>2.780001628266666</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1090503331691703</v>
+        <v>0.110368048443528</v>
       </c>
       <c r="T53">
-        <v>1.460746724461208</v>
+        <v>1.491178947887484</v>
       </c>
       <c r="U53">
         <v>0.1468</v>
       </c>
       <c r="V53">
-        <v>0.1467949835740212</v>
+        <v>0.1439720031206747</v>
       </c>
       <c r="W53">
-        <v>0.1252504964113337</v>
+        <v>0.125664909941885</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5659,7 +5659,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.8634999033765953</v>
+        <v>0.8468941360039685</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5667,22 +5667,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1183224164226737</v>
+        <v>0.1193324164226736</v>
       </c>
       <c r="C54">
-        <v>2.643710703465697</v>
+        <v>2.010585359678696</v>
       </c>
       <c r="D54">
-        <v>13.7473107034657</v>
+        <v>13.5584853596787</v>
       </c>
       <c r="E54">
-        <v>-11.6964</v>
+        <v>-11.2521</v>
       </c>
       <c r="F54">
-        <v>23.1036</v>
+        <v>23.5479</v>
       </c>
       <c r="G54">
         <v>12</v>
@@ -5703,37 +5703,37 @@
         <v>2.872333333333333</v>
       </c>
       <c r="M54">
-        <v>3.39160848</v>
+        <v>3.456831720000001</v>
       </c>
       <c r="N54">
-        <v>-0.5192751466666672</v>
+        <v>-0.5844983866666675</v>
       </c>
       <c r="O54">
-        <v>-0.08827677493333343</v>
+        <v>-0.09936472573333349</v>
       </c>
       <c r="P54">
-        <v>-0.4309983717333338</v>
+        <v>-0.485133660933334</v>
       </c>
       <c r="Q54">
-        <v>2.780001628266666</v>
+        <v>2.725866339066666</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.110368048443528</v>
+        <v>0.1117418367082839</v>
       </c>
       <c r="T54">
-        <v>1.491178947887484</v>
+        <v>1.522906159544664</v>
       </c>
       <c r="U54">
         <v>0.1468</v>
       </c>
       <c r="V54">
-        <v>0.1439720031206747</v>
+        <v>0.1412555502316053</v>
       </c>
       <c r="W54">
-        <v>0.125664909941885</v>
+        <v>0.1260636852260004</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5741,7 +5741,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.8468941360039685</v>
+        <v>0.8309150013623841</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5749,22 +5749,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1193324164226736</v>
+        <v>0.1203424164226736</v>
       </c>
       <c r="C55">
-        <v>2.010585359678696</v>
+        <v>1.382576930700136</v>
       </c>
       <c r="D55">
-        <v>13.5584853596787</v>
+        <v>13.37477693070013</v>
       </c>
       <c r="E55">
-        <v>-11.2521</v>
+        <v>-10.8078</v>
       </c>
       <c r="F55">
-        <v>23.5479</v>
+        <v>23.9922</v>
       </c>
       <c r="G55">
         <v>12</v>
@@ -5785,37 +5785,37 @@
         <v>2.872333333333333</v>
       </c>
       <c r="M55">
-        <v>3.456831720000001</v>
+        <v>3.52205496</v>
       </c>
       <c r="N55">
-        <v>-0.5844983866666675</v>
+        <v>-0.649721626666667</v>
       </c>
       <c r="O55">
-        <v>-0.09936472573333349</v>
+        <v>-0.1104526765333334</v>
       </c>
       <c r="P55">
-        <v>-0.485133660933334</v>
+        <v>-0.5392689501333336</v>
       </c>
       <c r="Q55">
-        <v>2.725866339066666</v>
+        <v>2.671731049866666</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1117418367082839</v>
+        <v>0.1131753548975945</v>
       </c>
       <c r="T55">
-        <v>1.522906159544664</v>
+        <v>1.556012815186939</v>
       </c>
       <c r="U55">
         <v>0.1468</v>
       </c>
       <c r="V55">
-        <v>0.1412555502316053</v>
+        <v>0.1386397067087978</v>
       </c>
       <c r="W55">
-        <v>0.1260636852260004</v>
+        <v>0.1264476910551485</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5823,7 +5823,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.8309150013623841</v>
+        <v>0.8155276865223401</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5831,22 +5831,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1203424164226736</v>
+        <v>0.1213524164226736</v>
       </c>
       <c r="C56">
-        <v>1.382576930700136</v>
+        <v>0.7594802046704245</v>
       </c>
       <c r="D56">
-        <v>13.37477693070013</v>
+        <v>13.19598020467043</v>
       </c>
       <c r="E56">
-        <v>-10.8078</v>
+        <v>-10.36349999999999</v>
       </c>
       <c r="F56">
-        <v>23.9922</v>
+        <v>24.4365</v>
       </c>
       <c r="G56">
         <v>12</v>
@@ -5867,37 +5867,37 @@
         <v>2.872333333333333</v>
       </c>
       <c r="M56">
-        <v>3.52205496</v>
+        <v>3.587278200000001</v>
       </c>
       <c r="N56">
-        <v>-0.649721626666667</v>
+        <v>-0.7149448666666673</v>
       </c>
       <c r="O56">
-        <v>-0.1104526765333334</v>
+        <v>-0.1215406273333335</v>
       </c>
       <c r="P56">
-        <v>-0.5392689501333336</v>
+        <v>-0.5934042393333339</v>
       </c>
       <c r="Q56">
-        <v>2.671731049866666</v>
+        <v>2.617595760666666</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1131753548975945</v>
+        <v>0.1146725850064299</v>
       </c>
       <c r="T56">
-        <v>1.556012815186939</v>
+        <v>1.590590877746649</v>
       </c>
       <c r="U56">
         <v>0.1468</v>
       </c>
       <c r="V56">
-        <v>0.1386397067087978</v>
+        <v>0.1361189847686378</v>
       </c>
       <c r="W56">
-        <v>0.1264476910551485</v>
+        <v>0.126817733035964</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5905,7 +5905,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.8155276865223401</v>
+        <v>0.800699910403752</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5913,22 +5913,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1213524164226736</v>
+        <v>0.1532768907681081</v>
       </c>
       <c r="C57">
-        <v>0.7594802046704245</v>
+        <v>-3.604497118483664</v>
       </c>
       <c r="D57">
-        <v>13.19598020467043</v>
+        <v>9.276302881516335</v>
       </c>
       <c r="E57">
-        <v>-10.36349999999999</v>
+        <v>-9.919199999999996</v>
       </c>
       <c r="F57">
-        <v>24.4365</v>
+        <v>24.8808</v>
       </c>
       <c r="G57">
         <v>12</v>
@@ -5949,45 +5949,45 @@
         <v>2.872333333333333</v>
       </c>
       <c r="M57">
-        <v>3.587278200000001</v>
+        <v>4.99606464</v>
       </c>
       <c r="N57">
-        <v>-0.7149448666666673</v>
+        <v>-2.123731306666667</v>
       </c>
       <c r="O57">
-        <v>-0.1215406273333335</v>
+        <v>-0.3610343221333334</v>
       </c>
       <c r="P57">
-        <v>-0.5934042393333339</v>
+        <v>-1.762696984533334</v>
       </c>
       <c r="Q57">
-        <v>2.617595760666666</v>
+        <v>1.448303015466666</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1146725850064299</v>
+        <v>0.1177707672689272</v>
       </c>
       <c r="T57">
-        <v>1.590590877746649</v>
+        <v>1.662142431153053</v>
       </c>
       <c r="U57">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V57">
-        <v>0.1361189847686378</v>
+        <v>0.09773625880602431</v>
       </c>
       <c r="W57">
-        <v>0.126817733035964</v>
+        <v>0.1811745592317503</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y57">
-        <v>0.800699910403752</v>
+        <v>0.5749191694472018</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5995,22 +5995,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1532768907681081</v>
+        <v>0.1548268907681082</v>
       </c>
       <c r="C58">
-        <v>-3.604497118483664</v>
+        <v>-4.1806753126159</v>
       </c>
       <c r="D58">
-        <v>9.276302881516335</v>
+        <v>9.144424687384101</v>
       </c>
       <c r="E58">
-        <v>-9.919199999999996</v>
+        <v>-9.474899999999995</v>
       </c>
       <c r="F58">
-        <v>24.8808</v>
+        <v>25.3251</v>
       </c>
       <c r="G58">
         <v>12</v>
@@ -6031,37 +6031,37 @@
         <v>2.872333333333333</v>
       </c>
       <c r="M58">
-        <v>4.99606464</v>
+        <v>5.08528008</v>
       </c>
       <c r="N58">
-        <v>-2.123731306666667</v>
+        <v>-2.212946746666667</v>
       </c>
       <c r="O58">
-        <v>-0.3610343221333334</v>
+        <v>-0.3762009469333334</v>
       </c>
       <c r="P58">
-        <v>-1.762696984533334</v>
+        <v>-1.836745799733334</v>
       </c>
       <c r="Q58">
-        <v>1.448303015466666</v>
+        <v>1.374254200266666</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1177707672689272</v>
+        <v>0.1194445060426232</v>
       </c>
       <c r="T58">
-        <v>1.662142431153053</v>
+        <v>1.700796906296147</v>
       </c>
       <c r="U58">
         <v>0.2008</v>
       </c>
       <c r="V58">
-        <v>0.09773625880602431</v>
+        <v>0.09602158759890106</v>
       </c>
       <c r="W58">
-        <v>0.1811745592317503</v>
+        <v>0.1815188652101407</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6069,7 +6069,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.5749191694472018</v>
+        <v>0.5648328682288297</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6077,22 +6077,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1548268907681082</v>
+        <v>0.1563768907681081</v>
       </c>
       <c r="C59">
-        <v>-4.1806753126159</v>
+        <v>-4.753156329164554</v>
       </c>
       <c r="D59">
-        <v>9.144424687384101</v>
+        <v>9.016243670835451</v>
       </c>
       <c r="E59">
-        <v>-9.474899999999995</v>
+        <v>-9.030599999999993</v>
       </c>
       <c r="F59">
-        <v>25.3251</v>
+        <v>25.7694</v>
       </c>
       <c r="G59">
         <v>12</v>
@@ -6113,37 +6113,37 @@
         <v>2.872333333333333</v>
       </c>
       <c r="M59">
-        <v>5.08528008</v>
+        <v>5.174495520000001</v>
       </c>
       <c r="N59">
-        <v>-2.212946746666667</v>
+        <v>-2.302162186666667</v>
       </c>
       <c r="O59">
-        <v>-0.3762009469333334</v>
+        <v>-0.3913675717333335</v>
       </c>
       <c r="P59">
-        <v>-1.836745799733334</v>
+        <v>-1.910794614933334</v>
       </c>
       <c r="Q59">
-        <v>1.374254200266666</v>
+        <v>1.300205385066666</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1194445060426232</v>
+        <v>0.1211979466626856</v>
       </c>
       <c r="T59">
-        <v>1.700796906296147</v>
+        <v>1.741292070731769</v>
       </c>
       <c r="U59">
         <v>0.2008</v>
       </c>
       <c r="V59">
-        <v>0.09602158759890106</v>
+        <v>0.09436604298512691</v>
       </c>
       <c r="W59">
-        <v>0.1815188652101407</v>
+        <v>0.1818512985685865</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6151,7 +6151,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.5648328682288297</v>
+        <v>0.5550943705007465</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6159,22 +6159,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1563768907681081</v>
+        <v>0.1579268907681081</v>
       </c>
       <c r="C60">
-        <v>-4.753156329164547</v>
+        <v>-5.322093493310096</v>
       </c>
       <c r="D60">
-        <v>9.016243670835451</v>
+        <v>8.891606506689902</v>
       </c>
       <c r="E60">
-        <v>-9.0306</v>
+        <v>-8.586299999999998</v>
       </c>
       <c r="F60">
-        <v>25.7694</v>
+        <v>26.2137</v>
       </c>
       <c r="G60">
         <v>12</v>
@@ -6195,37 +6195,37 @@
         <v>2.872333333333333</v>
       </c>
       <c r="M60">
-        <v>5.17449552</v>
+        <v>5.26371096</v>
       </c>
       <c r="N60">
-        <v>-2.302162186666667</v>
+        <v>-2.391377626666667</v>
       </c>
       <c r="O60">
-        <v>-0.3913675717333334</v>
+        <v>-0.4065341965333334</v>
       </c>
       <c r="P60">
-        <v>-1.910794614933333</v>
+        <v>-1.984843430133334</v>
       </c>
       <c r="Q60">
-        <v>1.300205385066667</v>
+        <v>1.226156569866666</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1211979466626856</v>
+        <v>0.1230369209715316</v>
       </c>
       <c r="T60">
-        <v>1.741292070731769</v>
+        <v>1.7837626090423</v>
       </c>
       <c r="U60">
         <v>0.2008</v>
       </c>
       <c r="V60">
-        <v>0.09436604298512694</v>
+        <v>0.09276661852775189</v>
       </c>
       <c r="W60">
-        <v>0.1818512985685865</v>
+        <v>0.1821724629996274</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6233,7 +6233,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.5550943705007465</v>
+        <v>0.545685991339717</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1579268907681081</v>
+        <v>0.1594768907681081</v>
       </c>
       <c r="C61">
-        <v>-5.322093493310096</v>
+        <v>-5.887631767793554</v>
       </c>
       <c r="D61">
-        <v>8.891606506689902</v>
+        <v>8.770368232206446</v>
       </c>
       <c r="E61">
-        <v>-8.586299999999998</v>
+        <v>-8.141999999999999</v>
       </c>
       <c r="F61">
-        <v>26.2137</v>
+        <v>26.658</v>
       </c>
       <c r="G61">
         <v>12</v>
@@ -6277,37 +6277,37 @@
         <v>2.872333333333333</v>
       </c>
       <c r="M61">
-        <v>5.26371096</v>
+        <v>5.352926399999999</v>
       </c>
       <c r="N61">
-        <v>-2.391377626666667</v>
+        <v>-2.480593066666666</v>
       </c>
       <c r="O61">
-        <v>-0.4065341965333334</v>
+        <v>-0.4217008213333333</v>
       </c>
       <c r="P61">
-        <v>-1.984843430133334</v>
+        <v>-2.058892245333333</v>
       </c>
       <c r="Q61">
-        <v>1.226156569866666</v>
+        <v>1.152107754666667</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1230369209715316</v>
+        <v>0.1249678439958199</v>
       </c>
       <c r="T61">
-        <v>1.7837626090423</v>
+        <v>1.828356674268357</v>
       </c>
       <c r="U61">
         <v>0.2008</v>
       </c>
       <c r="V61">
-        <v>0.09276661852775189</v>
+        <v>0.09122050821895604</v>
       </c>
       <c r="W61">
-        <v>0.1821724629996274</v>
+        <v>0.1824829219496336</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6315,7 +6315,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.545685991339717</v>
+        <v>0.5365912248173884</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6323,22 +6323,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1594768907681081</v>
+        <v>0.1610268907681081</v>
       </c>
       <c r="C62">
-        <v>-5.887631767793554</v>
+        <v>-6.44990831536245</v>
       </c>
       <c r="D62">
-        <v>8.770368232206446</v>
+        <v>8.65239168463755</v>
       </c>
       <c r="E62">
-        <v>-8.141999999999999</v>
+        <v>-7.697699999999998</v>
       </c>
       <c r="F62">
-        <v>26.658</v>
+        <v>27.1023</v>
       </c>
       <c r="G62">
         <v>12</v>
@@ -6359,37 +6359,37 @@
         <v>2.872333333333333</v>
       </c>
       <c r="M62">
-        <v>5.352926399999999</v>
+        <v>5.44214184</v>
       </c>
       <c r="N62">
-        <v>-2.480593066666666</v>
+        <v>-2.569808506666666</v>
       </c>
       <c r="O62">
-        <v>-0.4217008213333333</v>
+        <v>-0.4368674461333333</v>
       </c>
       <c r="P62">
-        <v>-2.058892245333333</v>
+        <v>-2.132941060533333</v>
       </c>
       <c r="Q62">
-        <v>1.152107754666667</v>
+        <v>1.078058939466667</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1249678439958199</v>
+        <v>0.1269977887136614</v>
       </c>
       <c r="T62">
-        <v>1.828356674268357</v>
+        <v>1.875237614634213</v>
       </c>
       <c r="U62">
         <v>0.2008</v>
       </c>
       <c r="V62">
-        <v>0.09122050821895604</v>
+        <v>0.08972509005143216</v>
       </c>
       <c r="W62">
-        <v>0.1824829219496336</v>
+        <v>0.1827832019176724</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6397,7 +6397,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.5365912248173884</v>
+        <v>0.5277946473613656</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6405,22 +6405,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1610268907681081</v>
+        <v>0.1625768907681081</v>
       </c>
       <c r="C63">
-        <v>-6.44990831536245</v>
+        <v>-7.009053016424232</v>
       </c>
       <c r="D63">
-        <v>8.65239168463755</v>
+        <v>8.537546983575764</v>
       </c>
       <c r="E63">
-        <v>-7.697699999999998</v>
+        <v>-7.253399999999999</v>
       </c>
       <c r="F63">
-        <v>27.1023</v>
+        <v>27.5466</v>
       </c>
       <c r="G63">
         <v>12</v>
@@ -6441,37 +6441,37 @@
         <v>2.872333333333333</v>
       </c>
       <c r="M63">
-        <v>5.44214184</v>
+        <v>5.53135728</v>
       </c>
       <c r="N63">
-        <v>-2.569808506666666</v>
+        <v>-2.659023946666667</v>
       </c>
       <c r="O63">
-        <v>-0.4368674461333333</v>
+        <v>-0.4520340709333334</v>
       </c>
       <c r="P63">
-        <v>-2.132941060533333</v>
+        <v>-2.206989875733333</v>
       </c>
       <c r="Q63">
-        <v>1.078058939466667</v>
+        <v>1.004010124266666</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1269977887136614</v>
+        <v>0.1291345726271788</v>
       </c>
       <c r="T63">
-        <v>1.875237614634213</v>
+        <v>1.92458597291406</v>
       </c>
       <c r="U63">
         <v>0.2008</v>
       </c>
       <c r="V63">
-        <v>0.08972509005143216</v>
+        <v>0.08827791117963486</v>
       </c>
       <c r="W63">
-        <v>0.1827832019176724</v>
+        <v>0.1830737954351293</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6479,7 +6479,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.5277946473613656</v>
+        <v>0.5192818304684403</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6487,22 +6487,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1625768907681081</v>
+        <v>0.1641268907681081</v>
       </c>
       <c r="C64">
-        <v>-7.009053016424232</v>
+        <v>-7.565188946014207</v>
       </c>
       <c r="D64">
-        <v>8.537546983575764</v>
+        <v>8.425711053985793</v>
       </c>
       <c r="E64">
-        <v>-7.253399999999999</v>
+        <v>-6.809099999999997</v>
       </c>
       <c r="F64">
-        <v>27.5466</v>
+        <v>27.9909</v>
       </c>
       <c r="G64">
         <v>12</v>
@@ -6523,37 +6523,37 @@
         <v>2.872333333333333</v>
       </c>
       <c r="M64">
-        <v>5.53135728</v>
+        <v>5.62057272</v>
       </c>
       <c r="N64">
-        <v>-2.659023946666667</v>
+        <v>-2.748239386666667</v>
       </c>
       <c r="O64">
-        <v>-0.4520340709333334</v>
+        <v>-0.4672006957333334</v>
       </c>
       <c r="P64">
-        <v>-2.206989875733333</v>
+        <v>-2.281038690933333</v>
       </c>
       <c r="Q64">
-        <v>1.004010124266666</v>
+        <v>0.9299613090666665</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1291345726271788</v>
+        <v>0.1313868583738593</v>
       </c>
       <c r="T64">
-        <v>1.92458597291406</v>
+        <v>1.976601810019845</v>
       </c>
       <c r="U64">
         <v>0.2008</v>
       </c>
       <c r="V64">
-        <v>0.08827791117963486</v>
+        <v>0.08687667449424383</v>
       </c>
       <c r="W64">
-        <v>0.1830737954351293</v>
+        <v>0.1833551637615558</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6561,7 +6561,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.5192818304684403</v>
+        <v>0.511039261730846</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6569,22 +6569,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1641268907681081</v>
+        <v>0.1656768907681082</v>
       </c>
       <c r="C65">
-        <v>-7.565188946014207</v>
+        <v>-8.118432813760506</v>
       </c>
       <c r="D65">
-        <v>8.425711053985793</v>
+        <v>8.316767186239494</v>
       </c>
       <c r="E65">
-        <v>-6.809099999999997</v>
+        <v>-6.364799999999995</v>
       </c>
       <c r="F65">
-        <v>27.9909</v>
+        <v>28.4352</v>
       </c>
       <c r="G65">
         <v>12</v>
@@ -6605,37 +6605,37 @@
         <v>2.872333333333333</v>
       </c>
       <c r="M65">
-        <v>5.62057272</v>
+        <v>5.70978816</v>
       </c>
       <c r="N65">
-        <v>-2.748239386666667</v>
+        <v>-2.837454826666667</v>
       </c>
       <c r="O65">
-        <v>-0.4672006957333334</v>
+        <v>-0.4823673205333335</v>
       </c>
       <c r="P65">
-        <v>-2.281038690933333</v>
+        <v>-2.355087506133334</v>
       </c>
       <c r="Q65">
-        <v>0.9299613090666665</v>
+        <v>0.8559124938666662</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1313868583738593</v>
+        <v>0.1337642711064665</v>
       </c>
       <c r="T65">
-        <v>1.976601810019845</v>
+        <v>2.031507415853731</v>
       </c>
       <c r="U65">
         <v>0.2008</v>
       </c>
       <c r="V65">
-        <v>0.08687667449424383</v>
+        <v>0.08551922645527125</v>
       </c>
       <c r="W65">
-        <v>0.1833551637615558</v>
+        <v>0.1836277393277815</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6643,7 +6643,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.511039261730846</v>
+        <v>0.5030542732663015</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6651,22 +6651,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1656768907681082</v>
+        <v>0.1902490493132376</v>
       </c>
       <c r="C66">
-        <v>-8.118432813760506</v>
+        <v>-9.977494093636089</v>
       </c>
       <c r="D66">
-        <v>8.316767186239494</v>
+        <v>6.902005906363911</v>
       </c>
       <c r="E66">
-        <v>-6.364799999999995</v>
+        <v>-5.920499999999997</v>
       </c>
       <c r="F66">
-        <v>28.4352</v>
+        <v>28.8795</v>
       </c>
       <c r="G66">
         <v>12</v>
@@ -6687,45 +6687,45 @@
         <v>2.872333333333333</v>
       </c>
       <c r="M66">
-        <v>5.70978816</v>
+        <v>6.8097861</v>
       </c>
       <c r="N66">
-        <v>-2.837454826666667</v>
+        <v>-3.937452766666667</v>
       </c>
       <c r="O66">
-        <v>-0.4823673205333335</v>
+        <v>-0.6693669703333335</v>
       </c>
       <c r="P66">
-        <v>-2.355087506133334</v>
+        <v>-3.268085796333334</v>
       </c>
       <c r="Q66">
-        <v>0.8559124938666662</v>
+        <v>-0.05708579633333377</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1337642711064665</v>
+        <v>0.1370551318384498</v>
       </c>
       <c r="T66">
-        <v>2.031507415853731</v>
+        <v>2.107508818439948</v>
       </c>
       <c r="U66">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.08551922645527125</v>
+        <v>0.07170514014627664</v>
       </c>
       <c r="W66">
-        <v>0.1836277393277815</v>
+        <v>0.218891927953508</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y66">
-        <v>0.5030542732663015</v>
+        <v>0.4217949420369214</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6733,22 +6733,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1902490493132376</v>
+        <v>0.1921490493132376</v>
       </c>
       <c r="C67">
-        <v>-9.977494093636089</v>
+        <v>-10.51140049206252</v>
       </c>
       <c r="D67">
-        <v>6.902005906363911</v>
+        <v>6.81239950793748</v>
       </c>
       <c r="E67">
-        <v>-5.920499999999997</v>
+        <v>-5.476199999999995</v>
       </c>
       <c r="F67">
-        <v>28.8795</v>
+        <v>29.3238</v>
       </c>
       <c r="G67">
         <v>12</v>
@@ -6769,37 +6769,37 @@
         <v>2.872333333333333</v>
       </c>
       <c r="M67">
-        <v>6.8097861</v>
+        <v>6.914552040000001</v>
       </c>
       <c r="N67">
-        <v>-3.937452766666667</v>
+        <v>-4.042218706666668</v>
       </c>
       <c r="O67">
-        <v>-0.6693669703333335</v>
+        <v>-0.6871771801333336</v>
       </c>
       <c r="P67">
-        <v>-3.268085796333334</v>
+        <v>-3.355041526533335</v>
       </c>
       <c r="Q67">
-        <v>-0.05708579633333377</v>
+        <v>-0.1440415265333348</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1370551318384498</v>
+        <v>0.1397391063042865</v>
       </c>
       <c r="T67">
-        <v>2.107508818439948</v>
+        <v>2.169494371923476</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.07170514014627664</v>
+        <v>0.07061869862890881</v>
       </c>
       <c r="W67">
-        <v>0.218891927953508</v>
+        <v>0.2191481108633033</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6807,7 +6807,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.4217949420369214</v>
+        <v>0.4154041095818164</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6815,22 +6815,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1921490493132376</v>
+        <v>0.1940490493132376</v>
       </c>
       <c r="C68">
-        <v>-10.51140049206252</v>
+        <v>-11.04301005070753</v>
       </c>
       <c r="D68">
-        <v>6.81239950793748</v>
+        <v>6.725089949292469</v>
       </c>
       <c r="E68">
-        <v>-5.476199999999995</v>
+        <v>-5.031899999999997</v>
       </c>
       <c r="F68">
-        <v>29.3238</v>
+        <v>29.7681</v>
       </c>
       <c r="G68">
         <v>12</v>
@@ -6851,37 +6851,37 @@
         <v>2.872333333333333</v>
       </c>
       <c r="M68">
-        <v>6.914552040000001</v>
+        <v>7.01931798</v>
       </c>
       <c r="N68">
-        <v>-4.042218706666668</v>
+        <v>-4.146984646666667</v>
       </c>
       <c r="O68">
-        <v>-0.6871771801333336</v>
+        <v>-0.7049873899333334</v>
       </c>
       <c r="P68">
-        <v>-3.355041526533335</v>
+        <v>-3.441997256733333</v>
       </c>
       <c r="Q68">
-        <v>-0.1440415265333348</v>
+        <v>-0.2309972567333332</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1397391063042865</v>
+        <v>0.1425857458892649</v>
       </c>
       <c r="T68">
-        <v>2.169494371923476</v>
+        <v>2.235236625618127</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.07061869862890881</v>
+        <v>0.06956468820161167</v>
       </c>
       <c r="W68">
-        <v>0.2191481108633033</v>
+        <v>0.21939664652206</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6889,7 +6889,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.4154041095818164</v>
+        <v>0.4092040482447745</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6897,22 +6897,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1940490493132376</v>
+        <v>0.1959490493132376</v>
       </c>
       <c r="C69">
-        <v>-11.04301005070753</v>
+        <v>-11.57240996284217</v>
       </c>
       <c r="D69">
-        <v>6.725089949292469</v>
+        <v>6.639990037157832</v>
       </c>
       <c r="E69">
-        <v>-5.031899999999997</v>
+        <v>-4.587599999999995</v>
       </c>
       <c r="F69">
-        <v>29.7681</v>
+        <v>30.2124</v>
       </c>
       <c r="G69">
         <v>12</v>
@@ -6933,37 +6933,37 @@
         <v>2.872333333333333</v>
       </c>
       <c r="M69">
-        <v>7.01931798</v>
+        <v>7.124083920000001</v>
       </c>
       <c r="N69">
-        <v>-4.146984646666667</v>
+        <v>-4.251750586666668</v>
       </c>
       <c r="O69">
-        <v>-0.7049873899333334</v>
+        <v>-0.7227975997333337</v>
       </c>
       <c r="P69">
-        <v>-3.441997256733333</v>
+        <v>-3.528952986933335</v>
       </c>
       <c r="Q69">
-        <v>-0.2309972567333332</v>
+        <v>-0.3179529869333351</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1425857458892649</v>
+        <v>0.1456103004483044</v>
       </c>
       <c r="T69">
-        <v>2.235236625618127</v>
+        <v>2.305087770168693</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.06956468820161167</v>
+        <v>0.06854167808099973</v>
       </c>
       <c r="W69">
-        <v>0.21939664652206</v>
+        <v>0.2196378723085003</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6971,7 +6971,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.4092040482447745</v>
+        <v>0.4031863416529394</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6979,22 +6979,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1959490493132376</v>
+        <v>0.1978490493132376</v>
       </c>
       <c r="C70">
-        <v>-11.57240996284217</v>
+        <v>-12.0996830634803</v>
       </c>
       <c r="D70">
-        <v>6.639990037157832</v>
+        <v>6.5570169365197</v>
       </c>
       <c r="E70">
-        <v>-4.587599999999995</v>
+        <v>-4.143299999999996</v>
       </c>
       <c r="F70">
-        <v>30.2124</v>
+        <v>30.6567</v>
       </c>
       <c r="G70">
         <v>12</v>
@@ -7015,37 +7015,37 @@
         <v>2.872333333333333</v>
       </c>
       <c r="M70">
-        <v>7.124083920000001</v>
+        <v>7.22884986</v>
       </c>
       <c r="N70">
-        <v>-4.251750586666668</v>
+        <v>-4.356516526666667</v>
       </c>
       <c r="O70">
-        <v>-0.7227975997333337</v>
+        <v>-0.7406078095333334</v>
       </c>
       <c r="P70">
-        <v>-3.528952986933335</v>
+        <v>-3.615908717133333</v>
       </c>
       <c r="Q70">
-        <v>-0.3179529869333351</v>
+        <v>-0.4049087171333334</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1456103004483044</v>
+        <v>0.1488299875595401</v>
       </c>
       <c r="T70">
-        <v>2.305087770168693</v>
+        <v>2.379445440174135</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.06854167808099973</v>
+        <v>0.06754832042765191</v>
       </c>
       <c r="W70">
-        <v>0.2196378723085003</v>
+        <v>0.2198721060431597</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7053,7 +7053,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.4031863416529394</v>
+        <v>0.3973430613391289</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7061,22 +7061,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1978490493132376</v>
+        <v>0.1997490493132376</v>
       </c>
       <c r="C71">
-        <v>-12.0996830634803</v>
+        <v>-12.62490809832114</v>
       </c>
       <c r="D71">
-        <v>6.5570169365197</v>
+        <v>6.476091901678862</v>
       </c>
       <c r="E71">
-        <v>-4.143299999999996</v>
+        <v>-3.698999999999995</v>
       </c>
       <c r="F71">
-        <v>30.6567</v>
+        <v>31.101</v>
       </c>
       <c r="G71">
         <v>12</v>
@@ -7097,37 +7097,37 @@
         <v>2.872333333333333</v>
       </c>
       <c r="M71">
-        <v>7.22884986</v>
+        <v>7.333615800000001</v>
       </c>
       <c r="N71">
-        <v>-4.356516526666667</v>
+        <v>-4.461282466666669</v>
       </c>
       <c r="O71">
-        <v>-0.7406078095333334</v>
+        <v>-0.7584180193333337</v>
       </c>
       <c r="P71">
-        <v>-3.615908717133333</v>
+        <v>-3.702864447333335</v>
       </c>
       <c r="Q71">
-        <v>-0.4049087171333334</v>
+        <v>-0.4918644473333349</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1488299875595401</v>
+        <v>0.1522643204781914</v>
       </c>
       <c r="T71">
-        <v>2.379445440174135</v>
+        <v>2.45876028817994</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.06754832042765191</v>
+        <v>0.0665833444215426</v>
       </c>
       <c r="W71">
-        <v>0.2198721060431597</v>
+        <v>0.2200996473854003</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7135,7 +7135,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.3973430613391289</v>
+        <v>0.3916667318914269</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7143,22 +7143,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1997490493132376</v>
+        <v>0.2016490493132376</v>
       </c>
       <c r="C72">
-        <v>-12.62490809832114</v>
+        <v>-13.1481599730192</v>
       </c>
       <c r="D72">
-        <v>6.476091901678862</v>
+        <v>6.397140026980806</v>
       </c>
       <c r="E72">
-        <v>-3.698999999999995</v>
+        <v>-3.254699999999993</v>
       </c>
       <c r="F72">
-        <v>31.101</v>
+        <v>31.5453</v>
       </c>
       <c r="G72">
         <v>12</v>
@@ -7179,37 +7179,37 @@
         <v>2.872333333333333</v>
       </c>
       <c r="M72">
-        <v>7.333615800000001</v>
+        <v>7.438381740000001</v>
       </c>
       <c r="N72">
-        <v>-4.461282466666669</v>
+        <v>-4.566048406666669</v>
       </c>
       <c r="O72">
-        <v>-0.7584180193333337</v>
+        <v>-0.7762282291333338</v>
       </c>
       <c r="P72">
-        <v>-3.702864447333335</v>
+        <v>-3.789820177533335</v>
       </c>
       <c r="Q72">
-        <v>-0.4918644473333349</v>
+        <v>-0.578820177533335</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1522643204781914</v>
+        <v>0.1559355039429566</v>
       </c>
       <c r="T72">
-        <v>2.45876028817994</v>
+        <v>2.543545125703386</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.0665833444215426</v>
+        <v>0.06564555083814058</v>
       </c>
       <c r="W72">
-        <v>0.2200996473854003</v>
+        <v>0.2203207791123664</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7217,7 +7217,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.3916667318914269</v>
+        <v>0.3861502990478857</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7225,22 +7225,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2016490493132376</v>
+        <v>0.2035490493132376</v>
       </c>
       <c r="C73">
-        <v>-13.14815997301919</v>
+        <v>-13.66950998444036</v>
       </c>
       <c r="D73">
-        <v>6.39714002698081</v>
+        <v>6.320090015559636</v>
       </c>
       <c r="E73">
-        <v>-3.2547</v>
+        <v>-2.810399999999998</v>
       </c>
       <c r="F73">
-        <v>31.5453</v>
+        <v>31.9896</v>
       </c>
       <c r="G73">
         <v>12</v>
@@ -7261,37 +7261,37 @@
         <v>2.872333333333333</v>
       </c>
       <c r="M73">
-        <v>7.43838174</v>
+        <v>7.543147680000001</v>
       </c>
       <c r="N73">
-        <v>-4.566048406666667</v>
+        <v>-4.670814346666667</v>
       </c>
       <c r="O73">
-        <v>-0.7762282291333334</v>
+        <v>-0.7940384389333335</v>
       </c>
       <c r="P73">
-        <v>-3.789820177533334</v>
+        <v>-3.876775907733333</v>
       </c>
       <c r="Q73">
-        <v>-0.5788201775333337</v>
+        <v>-0.6657759077333334</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1559355039429566</v>
+        <v>0.1598689147980622</v>
       </c>
       <c r="T73">
-        <v>2.543545125703385</v>
+        <v>2.634386023049935</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.0656455508381406</v>
+        <v>0.06473380707649974</v>
       </c>
       <c r="W73">
-        <v>0.2203207791123664</v>
+        <v>0.2205357682913614</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7299,7 +7299,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.3861502990478858</v>
+        <v>0.3807871004499985</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7307,22 +7307,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2035490493132376</v>
+        <v>0.2054490493132376</v>
       </c>
       <c r="C74">
-        <v>-13.66950998444036</v>
+        <v>-14.18902603540477</v>
       </c>
       <c r="D74">
-        <v>6.320090015559636</v>
+        <v>6.244873964595235</v>
       </c>
       <c r="E74">
-        <v>-2.810399999999998</v>
+        <v>-2.366099999999996</v>
       </c>
       <c r="F74">
-        <v>31.9896</v>
+        <v>32.4339</v>
       </c>
       <c r="G74">
         <v>12</v>
@@ -7343,37 +7343,37 @@
         <v>2.872333333333333</v>
       </c>
       <c r="M74">
-        <v>7.543147680000001</v>
+        <v>7.647913620000001</v>
       </c>
       <c r="N74">
-        <v>-4.670814346666667</v>
+        <v>-4.775580286666667</v>
       </c>
       <c r="O74">
-        <v>-0.7940384389333335</v>
+        <v>-0.8118486487333334</v>
       </c>
       <c r="P74">
-        <v>-3.876775907733333</v>
+        <v>-3.963731637933334</v>
       </c>
       <c r="Q74">
-        <v>-0.6657759077333334</v>
+        <v>-0.752731637933334</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1598689147980622</v>
+        <v>0.1640936894202126</v>
       </c>
       <c r="T74">
-        <v>2.634386023049935</v>
+        <v>2.731955875755488</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.06473380707649974</v>
+        <v>0.06384704259599974</v>
       </c>
       <c r="W74">
-        <v>0.2205357682913614</v>
+        <v>0.2207448673558633</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7381,7 +7381,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.3807871004499985</v>
+        <v>0.3755708387999985</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7389,22 +7389,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2054490493132376</v>
+        <v>0.2073490493132376</v>
       </c>
       <c r="C75">
-        <v>-14.18902603540477</v>
+        <v>-14.70677283427589</v>
       </c>
       <c r="D75">
-        <v>6.244873964595235</v>
+        <v>6.171427165724107</v>
       </c>
       <c r="E75">
-        <v>-2.366099999999996</v>
+        <v>-1.921799999999998</v>
       </c>
       <c r="F75">
-        <v>32.4339</v>
+        <v>32.8782</v>
       </c>
       <c r="G75">
         <v>12</v>
@@ -7425,37 +7425,37 @@
         <v>2.872333333333333</v>
       </c>
       <c r="M75">
-        <v>7.647913620000001</v>
+        <v>7.75267956</v>
       </c>
       <c r="N75">
-        <v>-4.775580286666667</v>
+        <v>-4.880346226666667</v>
       </c>
       <c r="O75">
-        <v>-0.8118486487333334</v>
+        <v>-0.8296588585333334</v>
       </c>
       <c r="P75">
-        <v>-3.963731637933334</v>
+        <v>-4.050687368133334</v>
       </c>
       <c r="Q75">
-        <v>-0.752731637933334</v>
+        <v>-0.8396873681333337</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1640936894202126</v>
+        <v>0.1686434467056054</v>
       </c>
       <c r="T75">
-        <v>2.731955875755488</v>
+        <v>2.837031101746084</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.06384704259599974</v>
+        <v>0.06298424472308084</v>
       </c>
       <c r="W75">
-        <v>0.2207448673558633</v>
+        <v>0.2209483150942975</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7463,7 +7463,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.3755708387999985</v>
+        <v>0.370495557194593</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7471,22 +7471,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2073490493132376</v>
+        <v>0.2092490493132376</v>
       </c>
       <c r="C76">
-        <v>-14.70677283427589</v>
+        <v>-15.22281208062907</v>
       </c>
       <c r="D76">
-        <v>6.171427165724107</v>
+        <v>6.099687919370925</v>
       </c>
       <c r="E76">
-        <v>-1.921799999999998</v>
+        <v>-1.477499999999999</v>
       </c>
       <c r="F76">
-        <v>32.8782</v>
+        <v>33.3225</v>
       </c>
       <c r="G76">
         <v>12</v>
@@ -7507,37 +7507,37 @@
         <v>2.872333333333333</v>
       </c>
       <c r="M76">
-        <v>7.75267956</v>
+        <v>7.8574455</v>
       </c>
       <c r="N76">
-        <v>-4.880346226666667</v>
+        <v>-4.985112166666667</v>
       </c>
       <c r="O76">
-        <v>-0.8296588585333334</v>
+        <v>-0.8474690683333335</v>
       </c>
       <c r="P76">
-        <v>-4.050687368133334</v>
+        <v>-4.137643098333333</v>
       </c>
       <c r="Q76">
-        <v>-0.8396873681333337</v>
+        <v>-0.9266430983333334</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1686434467056054</v>
+        <v>0.1735571845738297</v>
       </c>
       <c r="T76">
-        <v>2.837031101746084</v>
+        <v>2.950512345815927</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.06298424472308084</v>
+        <v>0.06214445479343976</v>
       </c>
       <c r="W76">
-        <v>0.2209483150942975</v>
+        <v>0.2211463375597069</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7545,7 +7545,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.370495557194593</v>
+        <v>0.3655556164319985</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7553,22 +7553,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2092490493132376</v>
+        <v>0.2111490493132376</v>
       </c>
       <c r="C77">
-        <v>-15.22281208062907</v>
+        <v>-15.73720263811907</v>
       </c>
       <c r="D77">
-        <v>6.099687919370925</v>
+        <v>6.029597361880936</v>
       </c>
       <c r="E77">
-        <v>-1.477499999999999</v>
+        <v>-1.033199999999994</v>
       </c>
       <c r="F77">
-        <v>33.3225</v>
+        <v>33.7668</v>
       </c>
       <c r="G77">
         <v>12</v>
@@ -7589,37 +7589,37 @@
         <v>2.872333333333333</v>
       </c>
       <c r="M77">
-        <v>7.8574455</v>
+        <v>7.962211440000001</v>
       </c>
       <c r="N77">
-        <v>-4.985112166666667</v>
+        <v>-5.089878106666667</v>
       </c>
       <c r="O77">
-        <v>-0.8474690683333335</v>
+        <v>-0.8652792781333335</v>
       </c>
       <c r="P77">
-        <v>-4.137643098333333</v>
+        <v>-4.224598828533334</v>
       </c>
       <c r="Q77">
-        <v>-0.9266430983333334</v>
+        <v>-1.013598828533334</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1735571845738297</v>
+        <v>0.1788804005977392</v>
       </c>
       <c r="T77">
-        <v>2.950512345815927</v>
+        <v>3.073450360224924</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.06214445479343976</v>
+        <v>0.06132676459878923</v>
       </c>
       <c r="W77">
-        <v>0.2211463375597069</v>
+        <v>0.2213391489076055</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7627,7 +7627,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.3655556164319985</v>
+        <v>0.3607456741105249</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7635,22 +7635,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2111490493132376</v>
+        <v>0.2130490493132376</v>
       </c>
       <c r="C78">
-        <v>-15.73720263811907</v>
+        <v>-16.25000069556463</v>
       </c>
       <c r="D78">
-        <v>6.029597361880936</v>
+        <v>5.961099304435374</v>
       </c>
       <c r="E78">
-        <v>-1.033199999999994</v>
+        <v>-0.5888999999999953</v>
       </c>
       <c r="F78">
-        <v>33.7668</v>
+        <v>34.2111</v>
       </c>
       <c r="G78">
         <v>12</v>
@@ -7671,37 +7671,37 @@
         <v>2.872333333333333</v>
       </c>
       <c r="M78">
-        <v>7.962211440000001</v>
+        <v>8.066977380000001</v>
       </c>
       <c r="N78">
-        <v>-5.089878106666667</v>
+        <v>-5.194644046666667</v>
       </c>
       <c r="O78">
-        <v>-0.8652792781333335</v>
+        <v>-0.8830894879333335</v>
       </c>
       <c r="P78">
-        <v>-4.224598828533334</v>
+        <v>-4.311554558733333</v>
       </c>
       <c r="Q78">
-        <v>-1.013598828533334</v>
+        <v>-1.100554558733334</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1788804005977392</v>
+        <v>0.184666504971554</v>
       </c>
       <c r="T78">
-        <v>3.073450360224924</v>
+        <v>3.207078636756443</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.06132676459878923</v>
+        <v>0.06053031311049327</v>
       </c>
       <c r="W78">
-        <v>0.2213391489076055</v>
+        <v>0.2215269521685457</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3607456741105249</v>
+        <v>0.3560606653558428</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7717,22 +7717,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2130490493132376</v>
+        <v>0.2149490493132376</v>
       </c>
       <c r="C79">
-        <v>-16.25000069556463</v>
+        <v>-16.76125991717664</v>
       </c>
       <c r="D79">
-        <v>5.961099304435374</v>
+        <v>5.894140082823355</v>
       </c>
       <c r="E79">
-        <v>-0.5888999999999953</v>
+        <v>-0.144599999999997</v>
       </c>
       <c r="F79">
-        <v>34.2111</v>
+        <v>34.6554</v>
       </c>
       <c r="G79">
         <v>12</v>
@@ -7753,37 +7753,37 @@
         <v>2.872333333333333</v>
       </c>
       <c r="M79">
-        <v>8.066977380000001</v>
+        <v>8.171743320000001</v>
       </c>
       <c r="N79">
-        <v>-5.194644046666667</v>
+        <v>-5.299409986666667</v>
       </c>
       <c r="O79">
-        <v>-0.8830894879333335</v>
+        <v>-0.9008996977333336</v>
       </c>
       <c r="P79">
-        <v>-4.311554558733333</v>
+        <v>-4.398510288933334</v>
       </c>
       <c r="Q79">
-        <v>-1.100554558733334</v>
+        <v>-1.187510288933334</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.184666504971554</v>
+        <v>0.1909786188338974</v>
       </c>
       <c r="T79">
-        <v>3.207078636756443</v>
+        <v>3.35285493842719</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.06053031311049327</v>
+        <v>0.05975428345523054</v>
       </c>
       <c r="W79">
-        <v>0.2215269521685457</v>
+        <v>0.2217099399612567</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7791,7 +7791,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.3560606653558428</v>
+        <v>0.3514957850307678</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7799,22 +7799,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2149490493132376</v>
+        <v>0.2168490493132376</v>
       </c>
       <c r="C80">
-        <v>-16.76125991717664</v>
+        <v>-17.2710315827739</v>
       </c>
       <c r="D80">
-        <v>5.894140082823355</v>
+        <v>5.828668417226102</v>
       </c>
       <c r="E80">
-        <v>-0.144599999999997</v>
+        <v>0.2997000000000014</v>
       </c>
       <c r="F80">
-        <v>34.6554</v>
+        <v>35.0997</v>
       </c>
       <c r="G80">
         <v>12</v>
@@ -7835,37 +7835,37 @@
         <v>2.872333333333333</v>
       </c>
       <c r="M80">
-        <v>8.171743320000001</v>
+        <v>8.276509259999999</v>
       </c>
       <c r="N80">
-        <v>-5.299409986666667</v>
+        <v>-5.404175926666666</v>
       </c>
       <c r="O80">
-        <v>-0.9008996977333336</v>
+        <v>-0.9187099075333333</v>
       </c>
       <c r="P80">
-        <v>-4.398510288933334</v>
+        <v>-4.485466019133332</v>
       </c>
       <c r="Q80">
-        <v>-1.187510288933334</v>
+        <v>-1.274466019133332</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1909786188338974</v>
+        <v>0.1978918863974163</v>
       </c>
       <c r="T80">
-        <v>3.35285493842719</v>
+        <v>3.512514697399914</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.05975428345523054</v>
+        <v>0.0589979001203542</v>
       </c>
       <c r="W80">
-        <v>0.2217099399612567</v>
+        <v>0.2218882951516205</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7873,7 +7873,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3514957850307678</v>
+        <v>0.3470464712962013</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7881,22 +7881,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2168490493132376</v>
+        <v>0.2187490493132376</v>
       </c>
       <c r="C81">
-        <v>-17.2710315827739</v>
+        <v>-17.77936471875647</v>
       </c>
       <c r="D81">
-        <v>5.828668417226102</v>
+        <v>5.764635281243538</v>
       </c>
       <c r="E81">
-        <v>0.2997000000000014</v>
+        <v>0.7440000000000069</v>
       </c>
       <c r="F81">
-        <v>35.0997</v>
+        <v>35.544</v>
       </c>
       <c r="G81">
         <v>12</v>
@@ -7917,37 +7917,37 @@
         <v>2.872333333333333</v>
       </c>
       <c r="M81">
-        <v>8.276509259999999</v>
+        <v>8.381275200000001</v>
       </c>
       <c r="N81">
-        <v>-5.404175926666666</v>
+        <v>-5.508941866666667</v>
       </c>
       <c r="O81">
-        <v>-0.9187099075333333</v>
+        <v>-0.9365201173333335</v>
       </c>
       <c r="P81">
-        <v>-4.485466019133332</v>
+        <v>-4.572421749333333</v>
       </c>
       <c r="Q81">
-        <v>-1.274466019133332</v>
+        <v>-1.361421749333334</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1978918863974163</v>
+        <v>0.2054964807172871</v>
       </c>
       <c r="T81">
-        <v>3.512514697399914</v>
+        <v>3.68814043226991</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.0589979001203542</v>
+        <v>0.05826042636884977</v>
       </c>
       <c r="W81">
-        <v>0.2218882951516205</v>
+        <v>0.2220621914622252</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7955,7 +7955,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3470464712962013</v>
+        <v>0.3427083904049987</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7963,22 +7963,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2187490493132376</v>
+        <v>0.2206490493132376</v>
       </c>
       <c r="C82">
-        <v>-17.77936471875647</v>
+        <v>-18.28630622053976</v>
       </c>
       <c r="D82">
-        <v>5.764635281243538</v>
+        <v>5.701993779460241</v>
       </c>
       <c r="E82">
-        <v>0.7440000000000069</v>
+        <v>1.188300000000005</v>
       </c>
       <c r="F82">
-        <v>35.544</v>
+        <v>35.9883</v>
       </c>
       <c r="G82">
         <v>12</v>
@@ -7999,37 +7999,37 @@
         <v>2.872333333333333</v>
       </c>
       <c r="M82">
-        <v>8.381275200000001</v>
+        <v>8.486041140000001</v>
       </c>
       <c r="N82">
-        <v>-5.508941866666667</v>
+        <v>-5.613707806666667</v>
       </c>
       <c r="O82">
-        <v>-0.9365201173333335</v>
+        <v>-0.9543303271333335</v>
       </c>
       <c r="P82">
-        <v>-4.572421749333333</v>
+        <v>-4.659377479533334</v>
       </c>
       <c r="Q82">
-        <v>-1.361421749333334</v>
+        <v>-1.448377479533334</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2054964807172871</v>
+        <v>0.2139015586497759</v>
       </c>
       <c r="T82">
-        <v>3.68814043226991</v>
+        <v>3.882253086599905</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.05826042636884977</v>
+        <v>0.05754116184577755</v>
       </c>
       <c r="W82">
-        <v>0.2220621914622252</v>
+        <v>0.2222317940367657</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8037,7 +8037,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3427083904049987</v>
+        <v>0.3384774226222209</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8045,22 +8045,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2206490493132376</v>
+        <v>0.2225490493132376</v>
       </c>
       <c r="C83">
-        <v>-18.28630622053976</v>
+        <v>-18.79190096709183</v>
       </c>
       <c r="D83">
-        <v>5.701993779460241</v>
+        <v>5.64069903290817</v>
       </c>
       <c r="E83">
-        <v>1.188300000000005</v>
+        <v>1.632600000000004</v>
       </c>
       <c r="F83">
-        <v>35.9883</v>
+        <v>36.4326</v>
       </c>
       <c r="G83">
         <v>12</v>
@@ -8081,37 +8081,37 @@
         <v>2.872333333333333</v>
       </c>
       <c r="M83">
-        <v>8.486041140000001</v>
+        <v>8.590807080000001</v>
       </c>
       <c r="N83">
-        <v>-5.613707806666667</v>
+        <v>-5.718473746666668</v>
       </c>
       <c r="O83">
-        <v>-0.9543303271333335</v>
+        <v>-0.9721405369333336</v>
       </c>
       <c r="P83">
-        <v>-4.659377479533334</v>
+        <v>-4.746333209733334</v>
       </c>
       <c r="Q83">
-        <v>-1.448377479533334</v>
+        <v>-1.535333209733334</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2139015586497759</v>
+        <v>0.223240534130319</v>
       </c>
       <c r="T83">
-        <v>3.882253086599905</v>
+        <v>4.097933813633233</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.05754116184577755</v>
+        <v>0.05683944035985343</v>
       </c>
       <c r="W83">
-        <v>0.2222317940367657</v>
+        <v>0.2223972599631466</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8119,7 +8119,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3384774226222209</v>
+        <v>0.3343496491756085</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8127,22 +8127,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2225490493132376</v>
+        <v>0.2244490493132376</v>
       </c>
       <c r="C84">
-        <v>-18.79190096709183</v>
+        <v>-19.29619192816174</v>
       </c>
       <c r="D84">
-        <v>5.64069903290817</v>
+        <v>5.580708071838269</v>
       </c>
       <c r="E84">
-        <v>1.632600000000004</v>
+        <v>2.076900000000009</v>
       </c>
       <c r="F84">
-        <v>36.4326</v>
+        <v>36.87690000000001</v>
       </c>
       <c r="G84">
         <v>12</v>
@@ -8163,37 +8163,37 @@
         <v>2.872333333333333</v>
       </c>
       <c r="M84">
-        <v>8.590807080000001</v>
+        <v>8.695573020000001</v>
       </c>
       <c r="N84">
-        <v>-5.718473746666668</v>
+        <v>-5.823239686666668</v>
       </c>
       <c r="O84">
-        <v>-0.9721405369333336</v>
+        <v>-0.9899507467333336</v>
       </c>
       <c r="P84">
-        <v>-4.746333209733334</v>
+        <v>-4.833288939933334</v>
       </c>
       <c r="Q84">
-        <v>-1.535333209733334</v>
+        <v>-1.622288939933334</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.223240534130319</v>
+        <v>0.2336782126085731</v>
       </c>
       <c r="T84">
-        <v>4.097933813633233</v>
+        <v>4.338988743846953</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.05683944035985343</v>
+        <v>0.05615462782539737</v>
       </c>
       <c r="W84">
-        <v>0.2223972599631466</v>
+        <v>0.2225587387587713</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8201,7 +8201,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3343496491756085</v>
+        <v>0.3303213401493963</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8209,22 +8209,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2244490493132376</v>
+        <v>0.2263490493132376</v>
       </c>
       <c r="C85">
-        <v>-19.29619192816174</v>
+        <v>-19.79922026473745</v>
       </c>
       <c r="D85">
-        <v>5.580708071838269</v>
+        <v>5.521979735262554</v>
       </c>
       <c r="E85">
-        <v>2.076900000000009</v>
+        <v>2.521200000000007</v>
       </c>
       <c r="F85">
-        <v>36.87690000000001</v>
+        <v>37.3212</v>
       </c>
       <c r="G85">
         <v>12</v>
@@ -8245,37 +8245,37 @@
         <v>2.872333333333333</v>
       </c>
       <c r="M85">
-        <v>8.695573020000001</v>
+        <v>8.800338960000001</v>
       </c>
       <c r="N85">
-        <v>-5.823239686666668</v>
+        <v>-5.928005626666668</v>
       </c>
       <c r="O85">
-        <v>-0.9899507467333336</v>
+        <v>-1.007760956533334</v>
       </c>
       <c r="P85">
-        <v>-4.833288939933334</v>
+        <v>-4.920244670133334</v>
       </c>
       <c r="Q85">
-        <v>-1.622288939933334</v>
+        <v>-1.709244670133334</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2336782126085731</v>
+        <v>0.2454206008966089</v>
       </c>
       <c r="T85">
-        <v>4.338988743846953</v>
+        <v>4.610175540337389</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.05615462782539737</v>
+        <v>0.05548612035128549</v>
       </c>
       <c r="W85">
-        <v>0.2225587387587713</v>
+        <v>0.2227163728211669</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8283,7 +8283,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3303213401493963</v>
+        <v>0.3263889432428558</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8291,22 +8291,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2263490493132376</v>
+        <v>0.2282490493132376</v>
       </c>
       <c r="C86">
-        <v>-19.79922026473744</v>
+        <v>-20.30102542322684</v>
       </c>
       <c r="D86">
-        <v>5.521979735262557</v>
+        <v>5.464474576773153</v>
       </c>
       <c r="E86">
-        <v>2.5212</v>
+        <v>2.965499999999999</v>
       </c>
       <c r="F86">
-        <v>37.3212</v>
+        <v>37.7655</v>
       </c>
       <c r="G86">
         <v>12</v>
@@ -8327,37 +8327,37 @@
         <v>2.872333333333333</v>
       </c>
       <c r="M86">
-        <v>8.800338959999999</v>
+        <v>8.9051049</v>
       </c>
       <c r="N86">
-        <v>-5.928005626666666</v>
+        <v>-6.032771566666666</v>
       </c>
       <c r="O86">
-        <v>-1.007760956533333</v>
+        <v>-1.025571166333333</v>
       </c>
       <c r="P86">
-        <v>-4.920244670133332</v>
+        <v>-5.007200400333333</v>
       </c>
       <c r="Q86">
-        <v>-1.709244670133332</v>
+        <v>-1.796200400333333</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2454206008966088</v>
+        <v>0.2587286409563827</v>
       </c>
       <c r="T86">
-        <v>4.610175540337385</v>
+        <v>4.917520576359879</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.05548612035128551</v>
+        <v>0.05483334246479979</v>
       </c>
       <c r="W86">
-        <v>0.2227163728211669</v>
+        <v>0.2228702978468002</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8365,7 +8365,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3263889432428559</v>
+        <v>0.3225490733223517</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8373,22 +8373,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2282490493132376</v>
+        <v>0.2301490493132376</v>
       </c>
       <c r="C87">
-        <v>-20.30102542322684</v>
+        <v>-20.80164522381463</v>
       </c>
       <c r="D87">
-        <v>5.464474576773153</v>
+        <v>5.408154776185369</v>
       </c>
       <c r="E87">
-        <v>2.965499999999999</v>
+        <v>3.409800000000004</v>
       </c>
       <c r="F87">
-        <v>37.7655</v>
+        <v>38.2098</v>
       </c>
       <c r="G87">
         <v>12</v>
@@ -8409,37 +8409,37 @@
         <v>2.872333333333333</v>
       </c>
       <c r="M87">
-        <v>8.9051049</v>
+        <v>9.009870840000001</v>
       </c>
       <c r="N87">
-        <v>-6.032771566666666</v>
+        <v>-6.137537506666668</v>
       </c>
       <c r="O87">
-        <v>-1.025571166333333</v>
+        <v>-1.043381376133333</v>
       </c>
       <c r="P87">
-        <v>-5.007200400333333</v>
+        <v>-5.094156130533334</v>
       </c>
       <c r="Q87">
-        <v>-1.796200400333333</v>
+        <v>-1.883156130533334</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2587286409563827</v>
+        <v>0.2739378295961243</v>
       </c>
       <c r="T87">
-        <v>4.917520576359879</v>
+        <v>5.26877204609987</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.05483334246479979</v>
+        <v>0.05419574545939514</v>
       </c>
       <c r="W87">
-        <v>0.2228702978468002</v>
+        <v>0.2230206432206746</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8447,7 +8447,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3225490733223517</v>
+        <v>0.3187985027023243</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8455,22 +8455,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2301490493132376</v>
+        <v>0.2320490493132376</v>
       </c>
       <c r="C88">
-        <v>-20.80164522381463</v>
+        <v>-21.30111594341101</v>
       </c>
       <c r="D88">
-        <v>5.408154776185369</v>
+        <v>5.352984056588993</v>
       </c>
       <c r="E88">
-        <v>3.409800000000004</v>
+        <v>3.854100000000003</v>
       </c>
       <c r="F88">
-        <v>38.2098</v>
+        <v>38.6541</v>
       </c>
       <c r="G88">
         <v>12</v>
@@ -8491,37 +8491,37 @@
         <v>2.872333333333333</v>
       </c>
       <c r="M88">
-        <v>9.009870840000001</v>
+        <v>9.11463678</v>
       </c>
       <c r="N88">
-        <v>-6.137537506666668</v>
+        <v>-6.242303446666666</v>
       </c>
       <c r="O88">
-        <v>-1.043381376133333</v>
+        <v>-1.061191585933333</v>
       </c>
       <c r="P88">
-        <v>-5.094156130533334</v>
+        <v>-5.181111860733333</v>
       </c>
       <c r="Q88">
-        <v>-1.883156130533334</v>
+        <v>-1.970111860733333</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2739378295961243</v>
+        <v>0.2914868934112108</v>
       </c>
       <c r="T88">
-        <v>5.26877204609987</v>
+        <v>5.674062203492167</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.05419574545939514</v>
+        <v>0.05357280585641359</v>
       </c>
       <c r="W88">
-        <v>0.2230206432206746</v>
+        <v>0.2231675323790577</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3187985027023243</v>
+        <v>0.3151341520965506</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8537,22 +8537,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2320490493132376</v>
+        <v>0.2339490493132376</v>
       </c>
       <c r="C89">
-        <v>-21.30111594341101</v>
+        <v>-21.79947239357455</v>
       </c>
       <c r="D89">
-        <v>5.352984056588993</v>
+        <v>5.298927606425448</v>
       </c>
       <c r="E89">
-        <v>3.854100000000003</v>
+        <v>4.298400000000001</v>
       </c>
       <c r="F89">
-        <v>38.6541</v>
+        <v>39.0984</v>
       </c>
       <c r="G89">
         <v>12</v>
@@ -8573,37 +8573,37 @@
         <v>2.872333333333333</v>
       </c>
       <c r="M89">
-        <v>9.11463678</v>
+        <v>9.21940272</v>
       </c>
       <c r="N89">
-        <v>-6.242303446666666</v>
+        <v>-6.347069386666666</v>
       </c>
       <c r="O89">
-        <v>-1.061191585933333</v>
+        <v>-1.079001795733333</v>
       </c>
       <c r="P89">
-        <v>-5.181111860733333</v>
+        <v>-5.268067590933333</v>
       </c>
       <c r="Q89">
-        <v>-1.970111860733333</v>
+        <v>-2.057067590933333</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2914868934112108</v>
+        <v>0.3119608011954784</v>
       </c>
       <c r="T89">
-        <v>5.674062203492167</v>
+        <v>6.146900720449849</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.05357280585641359</v>
+        <v>0.05296402397168162</v>
       </c>
       <c r="W89">
-        <v>0.2231675323790577</v>
+        <v>0.2233110831474775</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8611,7 +8611,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3151341520965506</v>
+        <v>0.3115530821863625</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8619,22 +8619,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2339490493132376</v>
+        <v>0.2358490493132376</v>
       </c>
       <c r="C90">
-        <v>-21.79947239357455</v>
+        <v>-22.29674799376087</v>
       </c>
       <c r="D90">
-        <v>5.298927606425448</v>
+        <v>5.245952006239127</v>
       </c>
       <c r="E90">
-        <v>4.298400000000001</v>
+        <v>4.742700000000006</v>
       </c>
       <c r="F90">
-        <v>39.0984</v>
+        <v>39.5427</v>
       </c>
       <c r="G90">
         <v>12</v>
@@ -8655,37 +8655,37 @@
         <v>2.872333333333333</v>
       </c>
       <c r="M90">
-        <v>9.21940272</v>
+        <v>9.324168660000002</v>
       </c>
       <c r="N90">
-        <v>-6.347069386666666</v>
+        <v>-6.451835326666668</v>
       </c>
       <c r="O90">
-        <v>-1.079001795733333</v>
+        <v>-1.096812005533334</v>
       </c>
       <c r="P90">
-        <v>-5.268067590933333</v>
+        <v>-5.355023321133334</v>
       </c>
       <c r="Q90">
-        <v>-2.057067590933333</v>
+        <v>-2.144023321133334</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3119608011954784</v>
+        <v>0.3361572376677947</v>
       </c>
       <c r="T90">
-        <v>6.146900720449849</v>
+        <v>6.705709876854381</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.05296402397168162</v>
+        <v>0.05236892257874136</v>
       </c>
       <c r="W90">
-        <v>0.2233110831474775</v>
+        <v>0.2234514080559328</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8693,7 +8693,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3115530821863625</v>
+        <v>0.3080524857573022</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8701,22 +8701,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2358490493132376</v>
+        <v>0.2377490493132376</v>
       </c>
       <c r="C91">
-        <v>-22.29674799376087</v>
+        <v>-22.79297484022099</v>
       </c>
       <c r="D91">
-        <v>5.245952006239127</v>
+        <v>5.194025159779009</v>
       </c>
       <c r="E91">
-        <v>4.742700000000006</v>
+        <v>5.187000000000005</v>
       </c>
       <c r="F91">
-        <v>39.5427</v>
+        <v>39.987</v>
       </c>
       <c r="G91">
         <v>12</v>
@@ -8737,37 +8737,37 @@
         <v>2.872333333333333</v>
       </c>
       <c r="M91">
-        <v>9.324168660000002</v>
+        <v>9.428934600000002</v>
       </c>
       <c r="N91">
-        <v>-6.451835326666668</v>
+        <v>-6.556601266666668</v>
       </c>
       <c r="O91">
-        <v>-1.096812005533334</v>
+        <v>-1.114622215333334</v>
       </c>
       <c r="P91">
-        <v>-5.355023321133334</v>
+        <v>-5.441979051333334</v>
       </c>
       <c r="Q91">
-        <v>-2.144023321133334</v>
+        <v>-2.230979051333334</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3361572376677947</v>
+        <v>0.3651929614345742</v>
       </c>
       <c r="T91">
-        <v>6.705709876854381</v>
+        <v>7.37628086453982</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.05236892257874136</v>
+        <v>0.05178704566119979</v>
       </c>
       <c r="W91">
-        <v>0.2234514080559328</v>
+        <v>0.2235886146330891</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8775,7 +8775,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3080524857573022</v>
+        <v>0.3046296803599988</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8783,22 +8783,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2377490493132376</v>
+        <v>0.2396490493132376</v>
       </c>
       <c r="C92">
-        <v>-22.79297484022099</v>
+        <v>-23.2881837708479</v>
       </c>
       <c r="D92">
-        <v>5.194025159779009</v>
+        <v>5.143116229152097</v>
       </c>
       <c r="E92">
-        <v>5.187000000000005</v>
+        <v>5.631300000000003</v>
       </c>
       <c r="F92">
-        <v>39.987</v>
+        <v>40.4313</v>
       </c>
       <c r="G92">
         <v>12</v>
@@ -8819,37 +8819,37 @@
         <v>2.872333333333333</v>
       </c>
       <c r="M92">
-        <v>9.428934600000002</v>
+        <v>9.53370054</v>
       </c>
       <c r="N92">
-        <v>-6.556601266666668</v>
+        <v>-6.661367206666666</v>
       </c>
       <c r="O92">
-        <v>-1.114622215333334</v>
+        <v>-1.132432425133333</v>
       </c>
       <c r="P92">
-        <v>-5.441979051333334</v>
+        <v>-5.528934781533333</v>
       </c>
       <c r="Q92">
-        <v>-2.230979051333334</v>
+        <v>-2.317934781533333</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3651929614345742</v>
+        <v>0.400681068260638</v>
       </c>
       <c r="T92">
-        <v>7.37628086453982</v>
+        <v>8.195867627266466</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.05178704566119979</v>
+        <v>0.05121795724734046</v>
       </c>
       <c r="W92">
-        <v>0.2235886146330891</v>
+        <v>0.2237228056810771</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8857,7 +8857,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3046296803599988</v>
+        <v>0.3012821014549439</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8865,22 +8865,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2396490493132376</v>
+        <v>0.2415490493132376</v>
       </c>
       <c r="C93">
-        <v>-23.2881837708479</v>
+        <v>-23.7824044262466</v>
       </c>
       <c r="D93">
-        <v>5.143116229152097</v>
+        <v>5.0931955737534</v>
       </c>
       <c r="E93">
-        <v>5.631300000000003</v>
+        <v>6.075600000000001</v>
       </c>
       <c r="F93">
-        <v>40.4313</v>
+        <v>40.8756</v>
       </c>
       <c r="G93">
         <v>12</v>
@@ -8901,37 +8901,37 @@
         <v>2.872333333333333</v>
       </c>
       <c r="M93">
-        <v>9.53370054</v>
+        <v>9.63846648</v>
       </c>
       <c r="N93">
-        <v>-6.661367206666666</v>
+        <v>-6.766133146666666</v>
       </c>
       <c r="O93">
-        <v>-1.132432425133333</v>
+        <v>-1.150242634933333</v>
       </c>
       <c r="P93">
-        <v>-5.528934781533333</v>
+        <v>-5.615890511733333</v>
       </c>
       <c r="Q93">
-        <v>-2.317934781533333</v>
+        <v>-2.404890511733333</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.400681068260638</v>
+        <v>0.4450412017932179</v>
       </c>
       <c r="T93">
-        <v>8.195867627266466</v>
+        <v>9.220351080674778</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.05121795724734046</v>
+        <v>0.05066124032073894</v>
       </c>
       <c r="W93">
-        <v>0.2237228056810771</v>
+        <v>0.2238540795323698</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8939,7 +8939,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3012821014549439</v>
+        <v>0.2980072960043467</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8947,22 +8947,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2415490493132376</v>
+        <v>0.2434490493132376</v>
       </c>
       <c r="C94">
-        <v>-23.7824044262466</v>
+        <v>-24.27566530728173</v>
       </c>
       <c r="D94">
-        <v>5.0931955737534</v>
+        <v>5.044234692718272</v>
       </c>
       <c r="E94">
-        <v>6.075600000000001</v>
+        <v>6.519900000000007</v>
       </c>
       <c r="F94">
-        <v>40.8756</v>
+        <v>41.3199</v>
       </c>
       <c r="G94">
         <v>12</v>
@@ -8983,37 +8983,37 @@
         <v>2.872333333333333</v>
       </c>
       <c r="M94">
-        <v>9.63846648</v>
+        <v>9.743232420000002</v>
       </c>
       <c r="N94">
-        <v>-6.766133146666666</v>
+        <v>-6.870899086666668</v>
       </c>
       <c r="O94">
-        <v>-1.150242634933333</v>
+        <v>-1.168052844733334</v>
       </c>
       <c r="P94">
-        <v>-5.615890511733333</v>
+        <v>-5.702846241933335</v>
       </c>
       <c r="Q94">
-        <v>-2.404890511733333</v>
+        <v>-2.491846241933335</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4450412017932179</v>
+        <v>0.5020756591922491</v>
       </c>
       <c r="T94">
-        <v>9.220351080674778</v>
+        <v>10.53754409219975</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.05066124032073894</v>
+        <v>0.05011649580116109</v>
       </c>
       <c r="W94">
-        <v>0.2238540795323698</v>
+        <v>0.2239825302900862</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.2980072960043467</v>
+        <v>0.2948029164774182</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9029,22 +9029,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2434490493132376</v>
+        <v>0.2453490493132376</v>
       </c>
       <c r="C95">
-        <v>-24.27566530728173</v>
+        <v>-24.76799382933758</v>
       </c>
       <c r="D95">
-        <v>5.044234692718272</v>
+        <v>4.996206170662425</v>
       </c>
       <c r="E95">
-        <v>6.519900000000007</v>
+        <v>6.964200000000005</v>
       </c>
       <c r="F95">
-        <v>41.3199</v>
+        <v>41.7642</v>
       </c>
       <c r="G95">
         <v>12</v>
@@ -9065,37 +9065,37 @@
         <v>2.872333333333333</v>
       </c>
       <c r="M95">
-        <v>9.743232420000002</v>
+        <v>9.847998360000002</v>
       </c>
       <c r="N95">
-        <v>-6.870899086666668</v>
+        <v>-6.975665026666668</v>
       </c>
       <c r="O95">
-        <v>-1.168052844733334</v>
+        <v>-1.185863054533334</v>
       </c>
       <c r="P95">
-        <v>-5.702846241933335</v>
+        <v>-5.789801972133334</v>
       </c>
       <c r="Q95">
-        <v>-2.491846241933335</v>
+        <v>-2.578801972133335</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5020756591922491</v>
+        <v>0.5781216023909573</v>
       </c>
       <c r="T95">
-        <v>10.53754409219975</v>
+        <v>12.29380144089971</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.05011649580116109</v>
+        <v>0.04958334159051044</v>
       </c>
       <c r="W95">
-        <v>0.2239825302900862</v>
+        <v>0.2241082480529576</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9103,7 +9103,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.2948029164774182</v>
+        <v>0.2916667152382967</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9111,22 +9111,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2453490493132376</v>
+        <v>0.2472490493132376</v>
       </c>
       <c r="C96">
-        <v>-24.76799382933758</v>
+        <v>-25.25941637350753</v>
       </c>
       <c r="D96">
-        <v>4.996206170662425</v>
+        <v>4.949083626492467</v>
       </c>
       <c r="E96">
-        <v>6.964200000000005</v>
+        <v>7.408500000000004</v>
       </c>
       <c r="F96">
-        <v>41.7642</v>
+        <v>42.2085</v>
       </c>
       <c r="G96">
         <v>12</v>
@@ -9147,37 +9147,37 @@
         <v>2.872333333333333</v>
       </c>
       <c r="M96">
-        <v>9.847998360000002</v>
+        <v>9.9527643</v>
       </c>
       <c r="N96">
-        <v>-6.975665026666668</v>
+        <v>-7.080430966666666</v>
       </c>
       <c r="O96">
-        <v>-1.185863054533334</v>
+        <v>-1.203673264333333</v>
       </c>
       <c r="P96">
-        <v>-5.789801972133334</v>
+        <v>-5.876757702333333</v>
       </c>
       <c r="Q96">
-        <v>-2.578801972133335</v>
+        <v>-2.665757702333333</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.5781216023909573</v>
+        <v>0.684585922869149</v>
       </c>
       <c r="T96">
-        <v>12.29380144089971</v>
+        <v>14.75256172907966</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.04958334159051044</v>
+        <v>0.04906141167903139</v>
       </c>
       <c r="W96">
-        <v>0.2241082480529576</v>
+        <v>0.2242313191260844</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9185,7 +9185,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2916667152382967</v>
+        <v>0.28859653928842</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9193,22 +9193,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2472490493132376</v>
+        <v>0.2491490493132376</v>
       </c>
       <c r="C97">
-        <v>-25.25941637350753</v>
+        <v>-25.74995833491377</v>
       </c>
       <c r="D97">
-        <v>4.949083626492467</v>
+        <v>4.90284166508624</v>
       </c>
       <c r="E97">
-        <v>7.408500000000004</v>
+        <v>7.852800000000009</v>
       </c>
       <c r="F97">
-        <v>42.2085</v>
+        <v>42.65280000000001</v>
       </c>
       <c r="G97">
         <v>12</v>
@@ -9229,37 +9229,37 @@
         <v>2.872333333333333</v>
       </c>
       <c r="M97">
-        <v>9.9527643</v>
+        <v>10.05753024</v>
       </c>
       <c r="N97">
-        <v>-7.080430966666666</v>
+        <v>-7.185196906666668</v>
       </c>
       <c r="O97">
-        <v>-1.203673264333333</v>
+        <v>-1.221483474133334</v>
       </c>
       <c r="P97">
-        <v>-5.876757702333333</v>
+        <v>-5.963713432533335</v>
       </c>
       <c r="Q97">
-        <v>-2.665757702333333</v>
+        <v>-2.752713432533335</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.684585922869149</v>
+        <v>0.8442824035864368</v>
       </c>
       <c r="T97">
-        <v>14.75256172907966</v>
+        <v>18.44070216134958</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.04906141167903139</v>
+        <v>0.04855035530737481</v>
       </c>
       <c r="W97">
-        <v>0.2242313191260844</v>
+        <v>0.224351826218521</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9267,7 +9267,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.28859653928842</v>
+        <v>0.2855903253374988</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9275,22 +9275,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2491490493132376</v>
+        <v>0.2510490493132376</v>
       </c>
       <c r="C98">
-        <v>-25.74995833491376</v>
+        <v>-26.23964416834311</v>
       </c>
       <c r="D98">
-        <v>4.90284166508624</v>
+        <v>4.857455831656889</v>
       </c>
       <c r="E98">
-        <v>7.852800000000002</v>
+        <v>8.2971</v>
       </c>
       <c r="F98">
-        <v>42.6528</v>
+        <v>43.0971</v>
       </c>
       <c r="G98">
         <v>12</v>
@@ -9311,37 +9311,37 @@
         <v>2.872333333333333</v>
       </c>
       <c r="M98">
-        <v>10.05753024</v>
+        <v>10.16229618</v>
       </c>
       <c r="N98">
-        <v>-7.185196906666667</v>
+        <v>-7.289962846666667</v>
       </c>
       <c r="O98">
-        <v>-1.221483474133333</v>
+        <v>-1.239293683933334</v>
       </c>
       <c r="P98">
-        <v>-5.963713432533333</v>
+        <v>-6.050669162733334</v>
       </c>
       <c r="Q98">
-        <v>-2.752713432533333</v>
+        <v>-2.839669162733334</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.8442824035864346</v>
+        <v>1.110443204781913</v>
       </c>
       <c r="T98">
-        <v>18.44070216134953</v>
+        <v>24.58760288179937</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.04855035530737482</v>
+        <v>0.04804983618049466</v>
       </c>
       <c r="W98">
-        <v>0.224351826218521</v>
+        <v>0.2244698486286394</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9349,7 +9349,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.285590325337499</v>
+        <v>0.2826460951793803</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9357,22 +9357,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2510490493132376</v>
+        <v>0.2529490493132376</v>
       </c>
       <c r="C99">
-        <v>-26.23964416834311</v>
+        <v>-26.72849743137157</v>
       </c>
       <c r="D99">
-        <v>4.857455831656889</v>
+        <v>4.812902568628425</v>
       </c>
       <c r="E99">
-        <v>8.2971</v>
+        <v>8.741399999999999</v>
       </c>
       <c r="F99">
-        <v>43.0971</v>
+        <v>43.5414</v>
       </c>
       <c r="G99">
         <v>12</v>
@@ -9393,37 +9393,37 @@
         <v>2.872333333333333</v>
       </c>
       <c r="M99">
-        <v>10.16229618</v>
+        <v>10.26706212</v>
       </c>
       <c r="N99">
-        <v>-7.289962846666667</v>
+        <v>-7.394728786666667</v>
       </c>
       <c r="O99">
-        <v>-1.239293683933334</v>
+        <v>-1.257103893733333</v>
       </c>
       <c r="P99">
-        <v>-6.050669162733334</v>
+        <v>-6.137624892933333</v>
       </c>
       <c r="Q99">
-        <v>-2.839669162733334</v>
+        <v>-2.926624892933333</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.110443204781913</v>
+        <v>1.642764807172869</v>
       </c>
       <c r="T99">
-        <v>24.58760288179937</v>
+        <v>36.88140432269906</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.04804983618049466</v>
+        <v>0.04755953172967328</v>
       </c>
       <c r="W99">
-        <v>0.2244698486286394</v>
+        <v>0.224585462418143</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9431,7 +9431,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2826460951793803</v>
+        <v>0.2797619513510193</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9439,22 +9439,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2529490493132376</v>
+        <v>0.2548490493132376</v>
       </c>
       <c r="C100">
-        <v>-26.72849743137157</v>
+        <v>-27.21654082513698</v>
       </c>
       <c r="D100">
-        <v>4.812902568628425</v>
+        <v>4.769159174863016</v>
       </c>
       <c r="E100">
-        <v>8.741399999999999</v>
+        <v>9.185700000000004</v>
       </c>
       <c r="F100">
-        <v>43.5414</v>
+        <v>43.9857</v>
       </c>
       <c r="G100">
         <v>12</v>
@@ -9475,37 +9475,37 @@
         <v>2.872333333333333</v>
       </c>
       <c r="M100">
-        <v>10.26706212</v>
+        <v>10.37182806</v>
       </c>
       <c r="N100">
-        <v>-7.394728786666667</v>
+        <v>-7.499494726666667</v>
       </c>
       <c r="O100">
-        <v>-1.257103893733333</v>
+        <v>-1.274914103533333</v>
       </c>
       <c r="P100">
-        <v>-6.137624892933333</v>
+        <v>-6.224580623133333</v>
       </c>
       <c r="Q100">
-        <v>-2.926624892933333</v>
+        <v>-3.013580623133333</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.642764807172869</v>
+        <v>3.239729614345738</v>
       </c>
       <c r="T100">
-        <v>36.88140432269906</v>
+        <v>73.76280864539812</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.04755953172967328</v>
+        <v>0.04707913241927255</v>
       </c>
       <c r="W100">
-        <v>0.224585462418143</v>
+        <v>0.2246987405755355</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9513,91 +9513,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2797619513510193</v>
+        <v>0.2769360730545444</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2548490493132376</v>
-      </c>
-      <c r="C101">
-        <v>-27.21654082513698</v>
-      </c>
-      <c r="D101">
-        <v>4.769159174863016</v>
-      </c>
-      <c r="E101">
-        <v>9.185700000000004</v>
-      </c>
-      <c r="F101">
-        <v>43.9857</v>
-      </c>
-      <c r="G101">
-        <v>12</v>
-      </c>
-      <c r="H101">
-        <v>9.630000000000001</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>6.083333333333333</v>
-      </c>
-      <c r="K101">
-        <v>3.211</v>
-      </c>
-      <c r="L101">
-        <v>2.872333333333333</v>
-      </c>
-      <c r="M101">
-        <v>10.37182806</v>
-      </c>
-      <c r="N101">
-        <v>-7.499494726666667</v>
-      </c>
-      <c r="O101">
-        <v>-1.274914103533333</v>
-      </c>
-      <c r="P101">
-        <v>-6.224580623133333</v>
-      </c>
-      <c r="Q101">
-        <v>-3.013580623133333</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.239729614345738</v>
-      </c>
-      <c r="T101">
-        <v>73.76280864539812</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.04707913241927255</v>
-      </c>
-      <c r="W101">
-        <v>0.2246987405755355</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.2769360730545444</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
